--- a/docs/dominio-metrico/migracion/cuestionarios/el-conde-de-sex.xlsx
+++ b/docs/dominio-metrico/migracion/cuestionarios/el-conde-de-sex.xlsx
@@ -21,25 +21,25 @@
     <t>Migración métrica · El conde de Sex</t>
   </si>
   <si>
-    <t>Para Rosa Bono · generado el 2026-09-19</t>
-  </si>
-  <si>
-    <t>El Excel tiene cinco pestañas. En tres de ellas hay que escribir —Responder, Confirmar y Desviaciones— y las otras dos son de consulta: Secuencias, con todo lo que tiene anotado tu obra, e Instrucciones, con este mismo texto. Solo hace falta escribir en las columnas de fondo amarillo, que son «Respuesta», «Excepciones / detalle» y «Comentario». El resto de columnas las genera el programa y las necesita tal cual para poder leer las respuestas, así que conviene no tocarlas.</t>
-  </si>
-  <si>
-    <t>En Responder están las preguntas que no hemos podido contestar con lo que ya tenías anotado. Cada fila corresponde a un pasaje y a una pregunta. Cuando la celda tiene desplegable, basta con elegir; cuando no, la columna «Cómo contestar» explica el formato. Las preguntas que se refieren a cada estrofa aparecen de dos maneras: si son pocas estrofas, hay una fila por estrofa; si son muchas, hay una sola fila cuya respuesta vale para todas, y las estrofas que se aparten de ella se anotan en «Excepciones / detalle» indicando los versos y la respuesta, por ejemplo «191–194: Cruzada · abab; 203–206: Cruzada · abab».</t>
-  </si>
-  <si>
-    <t>Las filas marcadas como Decidir señalan pasajes cuyo número de versos no encaja con la forma que tienen asignada. En ellas hay que elegir en el desplegable qué ocurre y explicarlo al lado. Si se trata de una laguna que no se contó, indica en qué verso está y cuántos versos faltan, porque los añadiremos a la numeración y todo lo que viene después se desplazará. Si lo que falla es el rango, escribe el rango correcto.</t>
-  </si>
-  <si>
-    <t>En Confirmar aparecen las respuestas que hemos rellenado nosotros a partir del término que elegiste en su día: la asonancia de un romance, el esquema de una octava real «regular», o que un endecasílabo suelto «puro» no lleva pareados. Solo hay que revisarlas. Si alguna no es así, elige «No es así» y escribe al lado lo que corresponde.</t>
+    <t>Para Rosa Bono · generado el 2026-09-20</t>
+  </si>
+  <si>
+    <t>El Excel tiene cinco pestañas. En tres de ellas hay que escribir —Responder, Confirmar y Desviaciones— y las otras dos son de consulta: Secuencias, con todo lo que tiene anotado tu obra, e Instrucciones, donde estás ahora. Solo hace falta escribir en las columnas de fondo amarillo, que son «Respuesta», «Excepciones / detalle» y «Comentario». El resto de columnas las genera el programa y las necesita tal cual para poder leer las respuestas, así que conviene no tocarlas.</t>
+  </si>
+  <si>
+    <t>En Responder están las preguntas que no he podido contestar con lo que ya tenías anotado. Cada fila corresponde a un pasaje y a una pregunta. Cuando la celda tiene desplegable, basta con elegir; cuando no, la columna «Cómo contestar» explica el formato. Las preguntas que se refieren a cada estrofa aparecen de dos maneras: si son pocas estrofas, hay una fila por estrofa; si son muchas, hay una sola fila cuya respuesta vale para todas, y las estrofas que se aparten de ella se anotan en «Excepciones / detalle» indicando los versos y la respuesta, por ejemplo «191–194: Cruzada · abab; 203–206: Cruzada · abab».</t>
+  </si>
+  <si>
+    <t>Las filas marcadas como Decidir señalan pasajes cuyo número de versos no encaja con la forma que tienen asignada. En ellas hay que elegir en el desplegable qué ocurre y explicarlo al lado. Si se trata de una laguna que no se contó, indica en qué verso está y cuántos versos faltan, porque los añadiré a la numeración y todo lo que viene después se desplazará. Si lo que falla es el rango, escribe el rango correcto.</t>
+  </si>
+  <si>
+    <t>En Confirmar aparecen las respuestas que he rellenado yo a partir del término que elegiste en su día: la asonancia de un romance, el esquema de una octava real «regular», o que un endecasílabo suelto «puro» no lleva pareados. Solo hay que revisarlas. Si alguna no es así, elige «No es así» y escribe al lado lo que corresponde.</t>
   </si>
   <si>
     <t>En Desviaciones están los versos hipométricos e hipermétricos, las rimas defectuosas y las lagunas que anotaste, con tus notas, y cómo quedan en el modelo nuevo. Se trasladan tal cual. Si tienes a mano el número de sílabas de algún verso hipométrico o hipermétrico, ponlo en la columna «Sílabas»; si no, se registra simplemente que el verso tiene menos o más sílabas de las que le tocan, sin dar una cifra.</t>
   </si>
   <si>
-    <t>Si algo no está claro o no sabes cómo contestarlo, pregúntaselo a David antes de dejarlo a medias. Una vez hecha la migración podrás ver cada secuencia de tu obra con el editor nuevo en el dashboard y corregir allí lo que haga falta.</t>
+    <t>Si algo no está claro o no sabes cómo contestarlo, pregúntamelo antes de dejarlo a medias. Una vez hecha la migración podrás ver cada secuencia de tu obra con el editor nuevo en el dashboard y comprobar allí que la migración no dejó ningún hueco.</t>
   </si>
   <si>
     <t>Cuando no hay desplegable, los formatos son estos:</t>
@@ -141,7 +141,7 @@
     <t>Romance · Octosílabo</t>
   </si>
   <si>
-    <t>Tiene 189 versos, y un romance no puede tener un número impar: en algún punto falta o sobra un verso. Hay que localizarlo y decir si se trata de una laguna, en cuyo caso renumeraremos la obra a partir de ahí, o de un error en el rango, en cuyo caso hace falta el rango correcto.</t>
+    <t>Tiene 189 versos, y un romance octosílabo no puede tener un número impar: en algún punto falta o sobra un verso. Hay que localizarlo y decir si se trata de una laguna, en cuyo caso renumeraré la obra a partir de ahí, o de un error en el rango, en cuyo caso hace falta el rango correcto.</t>
   </si>
   <si>
     <t/>
@@ -600,7 +600,7 @@
     <t>Espinela</t>
   </si>
   <si>
-    <t>Revisar: Tiene 189 versos, y un romance no puede tener un número impar: en algún punto falta o sobra un verso. Hay que localizarlo y decir si se trata de una laguna, en cuyo caso renumeraremos la obra a partir de ahí, o de un error en el rango, en cuyo caso hace falta el rango correcto.</t>
+    <t>Revisar: Tiene 189 versos, y un romance octosílabo no puede tener un número impar: en algún punto falta o sobra un verso. Hay que localizarlo y decir si se trata de una laguna, en cuyo caso renumeraré la obra a partir de ahí, o de un error en el rango, en cuyo caso hace falta el rango correcto.</t>
   </si>
 </sst>
 </file>

--- a/docs/dominio-metrico/migracion/cuestionarios/el-conde-de-sex.xlsx
+++ b/docs/dominio-metrico/migracion/cuestionarios/el-conde-de-sex.xlsx
@@ -33,10 +33,10 @@
     <t>Las filas marcadas como Decidir señalan pasajes cuyo número de versos no encaja con la forma que tienen asignada. En ellas hay que elegir en el desplegable qué ocurre y explicarlo al lado. Si se trata de una laguna que no se contó, indica en qué verso está y cuántos versos faltan, porque los añadiré a la numeración y todo lo que viene después se desplazará. Si lo que falla es el rango, escribe el rango correcto.</t>
   </si>
   <si>
-    <t>En Confirmar aparecen las respuestas que he rellenado yo a partir del término que elegiste en su día: la asonancia de un romance, el esquema de una octava real «regular», o que un endecasílabo suelto «puro» no lleva pareados. Solo hay que revisarlas. Si alguna no es así, elige «No es así» y escribe al lado lo que corresponde.</t>
-  </si>
-  <si>
-    <t>En Desviaciones están los versos hipométricos e hipermétricos, las rimas defectuosas y las lagunas que anotaste, con tus notas, y cómo quedan en el modelo nuevo. Se trasladan tal cual. Si tienes a mano el número de sílabas de algún verso hipométrico o hipermétrico, ponlo en la columna «Sílabas»; si no, se registra simplemente que el verso tiene menos o más sílabas de las que le tocan, sin dar una cifra.</t>
+    <t>En Confirmar aparecen las respuestas que he rellenado yo a partir del término que elegiste en su día: la asonancia de un romance, el esquema de una octava real «regular», o que un endecasílabo suelto «puro» no lleva pareados. Ahí van también los tramos que vuelven a ser una sola secuencia. Solo hay que revisarlas. Si alguna no es así, elige «No es así» y escribe al lado lo que corresponde.</t>
+  </si>
+  <si>
+    <t>En Desviaciones están los versos hipométricos e hipermétricos, las rimas defectuosas y las lagunas que anotaste, con tus notas, y cómo quedan en el modelo nuevo. Se trasladan tal cual, así que basta con revisarlas: la columna «¿Correcto?» tiene el mismo desplegable que la pestaña anterior y solo hay que tocarla si algo no queda como digo. La columna «Sílabas del verso» es únicamente para los versos hipométricos e hipermétricos, por si tienes a mano cuántas sílabas mide el verso; si no la rellenas, se registra que tiene menos o más de las que le tocan, sin dar una cifra. En las demás filas esa celda está apagada.</t>
   </si>
   <si>
     <t>Si algo no está claro o no sabes cómo contestarlo, pregúntamelo antes de dejarlo a medias. Una vez hecha la migración podrás ver cada secuencia de tu obra con el editor nuevo en el dashboard y comprobar allí que la migración no dejó ningún hueco.</t>
@@ -492,7 +492,7 @@
     <t>Cómo queda</t>
   </si>
   <si>
-    <t>Sílabas</t>
+    <t>Sílabas del verso</t>
   </si>
   <si>
     <t>#</t>
@@ -2401,7 +2401,7 @@
     <col min="4" max="4" width="18" customWidth="1"/>
     <col min="5" max="5" width="44" customWidth="1"/>
     <col min="6" max="6" width="40" customWidth="1"/>
-    <col min="7" max="7" width="10" customWidth="1"/>
+    <col min="7" max="7" width="12" customWidth="1"/>
     <col min="8" max="8" width="18" customWidth="1"/>
     <col min="9" max="9" width="30" customWidth="1"/>
     <col min="10" max="10" width="14" customWidth="1"/>

--- a/docs/dominio-metrico/migracion/cuestionarios/el-conde-de-sex.xlsx
+++ b/docs/dominio-metrico/migracion/cuestionarios/el-conde-de-sex.xlsx
@@ -21,7 +21,7 @@
     <t>Migración métrica · El conde de Sex</t>
   </si>
   <si>
-    <t>Para Rosa Bono · generado el 2026-09-20</t>
+    <t>Para Rosa Bono · generado el 2026-09-21</t>
   </si>
   <si>
     <t>El Excel tiene cinco pestañas. En tres de ellas hay que escribir —Responder, Confirmar y Desviaciones— y las otras dos son de consulta: Secuencias, con todo lo que tiene anotado tu obra, e Instrucciones, donde estás ahora. Solo hace falta escribir en las columnas de fondo amarillo, que son «Respuesta», «Excepciones / detalle» y «Comentario». El resto de columnas las genera el programa y las necesita tal cual para poder leer las respuestas, así que conviene no tocarlas.</t>
@@ -141,7 +141,7 @@
     <t>Romance · Octosílabo</t>
   </si>
   <si>
-    <t>Tiene 189 versos, y un romance octosílabo no puede tener un número impar: en algún punto falta o sobra un verso. Hay que localizarlo y decir si se trata de una laguna, en cuyo caso renumeraré la obra a partir de ahí, o de un error en el rango, en cuyo caso hace falta el rango correcto.</t>
+    <t>Tiene 189 versos, y un romance octosílabo no puede tener un número impar: en algún punto falta o sobra un verso. Hay que localizarlo y decir si se trata de una laguna, en cuyo caso renumeraré la obra a partir de ahí, o de un error en el rango, en cuyo caso hace falta el rango correcto. Las preguntas que dependen de cómo se reparta en estrofas te las haré cuando esto esté claro.</t>
   </si>
   <si>
     <t/>
@@ -234,7 +234,7 @@
     <t>Medida de los versos · estrofa 1 (vv. 1887–1888)</t>
   </si>
   <si>
-    <t>Escribe el número de sílabas de cada verso, en orden y separados por espacios («7 11 7 7 11»)</t>
+    <t>Indica 2, en orden y separadas por punto y coma, eligiendo entre: Tetrasílabo · Pentasílabo · Hexasílabo · Heptasílabo · Octosílabo · Endecasílabo · Dodecasílabo compuesto 6 + 6 · Dodecasílabo · Alejandrino</t>
   </si>
   <si>
     <t>U|cb94c0f3-5ba7-49e7-a0ea-ba1ca41f070a|d87da020-d071-4ce2-b906-31f1529a4664|1887</t>

--- a/docs/dominio-metrico/migracion/cuestionarios/el-conde-de-sex.xlsx
+++ b/docs/dominio-metrico/migracion/cuestionarios/el-conde-de-sex.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="658" uniqueCount="195">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="679" uniqueCount="207">
   <si>
     <t>Migración métrica · El conde de Sex</t>
   </si>
@@ -69,6 +69,9 @@
     <t>Tipología 1 · ababa</t>
   </si>
   <si>
+    <t>a</t>
+  </si>
+  <si>
     <t>Es correcto</t>
   </si>
   <si>
@@ -81,27 +84,84 @@
     <t>Tipología 2 · abbab</t>
   </si>
   <si>
+    <t>a-a</t>
+  </si>
+  <si>
     <t>No es así (lo corrijo al lado)</t>
   </si>
   <si>
     <t>Tipología 3 · abaab</t>
   </si>
   <si>
+    <t>a-e</t>
+  </si>
+  <si>
     <t>Tipología 4 · aabab</t>
   </si>
   <si>
+    <t>a-o</t>
+  </si>
+  <si>
     <t>Tipología 5 · aabba</t>
   </si>
   <si>
+    <t>e</t>
+  </si>
+  <si>
     <t>Tipología 6 · abbaa</t>
   </si>
   <si>
+    <t>e-a</t>
+  </si>
+  <si>
     <t>Tipología 7 · ababb</t>
   </si>
   <si>
+    <t>e-e</t>
+  </si>
+  <si>
     <t>Tipología 8 · abbba</t>
   </si>
   <si>
+    <t>e-o</t>
+  </si>
+  <si>
+    <t>i</t>
+  </si>
+  <si>
+    <t>i-a</t>
+  </si>
+  <si>
+    <t>i-e</t>
+  </si>
+  <si>
+    <t>i-o</t>
+  </si>
+  <si>
+    <t>o</t>
+  </si>
+  <si>
+    <t>o-a</t>
+  </si>
+  <si>
+    <t>o-e</t>
+  </si>
+  <si>
+    <t>o-o</t>
+  </si>
+  <si>
+    <t>u</t>
+  </si>
+  <si>
+    <t>u-a</t>
+  </si>
+  <si>
+    <t>u-e</t>
+  </si>
+  <si>
+    <t>u-o</t>
+  </si>
+  <si>
     <t>Tipo</t>
   </si>
   <si>
@@ -228,16 +288,13 @@
     <t>1887–1888</t>
   </si>
   <si>
-    <t>Pareado · De cualquier medida</t>
-  </si>
-  <si>
-    <t>Medida de los versos · estrofa 1 (vv. 1887–1888)</t>
-  </si>
-  <si>
-    <t>Indica 2, en orden y separadas por punto y coma, eligiendo entre: Tetrasílabo · Pentasílabo · Hexasílabo · Heptasílabo · Octosílabo · Endecasílabo · Dodecasílabo compuesto 6 + 6 · Dodecasílabo · Alejandrino</t>
-  </si>
-  <si>
-    <t>U|cb94c0f3-5ba7-49e7-a0ea-ba1ca41f070a|d87da020-d071-4ce2-b906-31f1529a4664|1887</t>
+    <t>Pareado · Isométrico</t>
+  </si>
+  <si>
+    <t>Vocales de la asonancia</t>
+  </si>
+  <si>
+    <t>R|cb94c0f3-5ba7-49e7-a0ea-ba1ca41f070a|da2e8262-3dbf-43d4-ba62-f492fa06dc8b</t>
   </si>
   <si>
     <t>Pregunta</t>
@@ -255,12 +312,6 @@
     <t>1–114</t>
   </si>
   <si>
-    <t>Vocales de la asonancia</t>
-  </si>
-  <si>
-    <t>a-o</t>
-  </si>
-  <si>
     <t>romance_a-o</t>
   </si>
   <si>
@@ -309,9 +360,6 @@
     <t>365–816</t>
   </si>
   <si>
-    <t>i-o</t>
-  </si>
-  <si>
     <t>romance_i-o</t>
   </si>
   <si>
@@ -327,9 +375,6 @@
     <t>995–1076</t>
   </si>
   <si>
-    <t>e-o</t>
-  </si>
-  <si>
     <t>romance_e-o</t>
   </si>
   <si>
@@ -423,16 +468,13 @@
     <t>1635–1886</t>
   </si>
   <si>
-    <t>e-a</t>
-  </si>
-  <si>
     <t>romance_e-a</t>
   </si>
   <si>
     <t>C|7d55b05a-6034-4056-9d8d-8c741592e584</t>
   </si>
   <si>
-    <t>aa · Consonante</t>
+    <t>Esquema de rima: aa · Consonante; Medida de los versos: Endecasílabo</t>
   </si>
   <si>
     <t>pareado_endecasilabo</t>
@@ -444,9 +486,6 @@
     <t>1889–2030</t>
   </si>
   <si>
-    <t>e-e</t>
-  </si>
-  <si>
     <t>romance_e-e</t>
   </si>
   <si>
@@ -462,9 +501,6 @@
     <t>2317–2436</t>
   </si>
   <si>
-    <t>o-o</t>
-  </si>
-  <si>
     <t>romance_o-o</t>
   </si>
   <si>
@@ -582,10 +618,10 @@
     <t>Pareado</t>
   </si>
   <si>
-    <t>De cualquier medida</t>
-  </si>
-  <si>
-    <t>Falta: Medida de los versos</t>
+    <t>Isométrico</t>
+  </si>
+  <si>
+    <t>Falta: Vocales de la asonancia</t>
   </si>
   <si>
     <t>2031–2140</t>
@@ -1100,13 +1136,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="4" width="40" customWidth="1"/>
+    <col min="1" max="5" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>13</v>
       </c>
@@ -1119,8 +1155,11 @@
       <c r="D1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>14</v>
       </c>
@@ -1133,49 +1172,133 @@
       <c r="D2" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="4" spans="3:3" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="E3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="4" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C4" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="5" spans="3:3" x14ac:dyDescent="0.25">
+        <v>24</v>
+      </c>
+      <c r="D4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C5" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="6" spans="3:3" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+      <c r="D5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="6" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C6" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="7" spans="3:3" x14ac:dyDescent="0.25">
+        <v>28</v>
+      </c>
+      <c r="D6" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="7" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C7" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="8" spans="3:3" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+      <c r="D7" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="8" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C8" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="9" spans="3:3" x14ac:dyDescent="0.25">
+        <v>32</v>
+      </c>
+      <c r="D8" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="9" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C9" t="s">
-        <v>27</v>
+        <v>34</v>
+      </c>
+      <c r="D9" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="10" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D10" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="11" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D11" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="12" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D12" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="13" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D13" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="14" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D14" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="15" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D15" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="16" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D16" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="17" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D17" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="18" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D18" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="19" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D19" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="20" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D20" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="21" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D21" t="s">
+        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -1202,393 +1325,396 @@
   <sheetData>
     <row r="1" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>29</v>
+        <v>49</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>36</v>
+        <v>56</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>37</v>
+        <v>57</v>
       </c>
     </row>
     <row r="2" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>41</v>
+        <v>61</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>43</v>
+        <v>63</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="J2" s="7" t="s">
-        <v>44</v>
+        <v>64</v>
       </c>
     </row>
     <row r="3" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>47</v>
+        <v>67</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>48</v>
+        <v>68</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>49</v>
+        <v>69</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="J3" s="7" t="s">
-        <v>50</v>
+        <v>70</v>
       </c>
     </row>
     <row r="4" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>51</v>
+        <v>71</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>53</v>
+        <v>73</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>49</v>
+        <v>69</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="J4" s="7" t="s">
-        <v>54</v>
+        <v>74</v>
       </c>
     </row>
     <row r="5" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>51</v>
+        <v>71</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>49</v>
+        <v>69</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="J5" s="7" t="s">
-        <v>56</v>
+        <v>76</v>
       </c>
     </row>
     <row r="6" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>51</v>
+        <v>71</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>57</v>
+        <v>77</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>49</v>
+        <v>69</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="J6" s="7" t="s">
-        <v>58</v>
+        <v>78</v>
       </c>
     </row>
     <row r="7" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>51</v>
+        <v>71</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>59</v>
+        <v>79</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>49</v>
+        <v>69</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="J7" s="7" t="s">
-        <v>60</v>
+        <v>80</v>
       </c>
     </row>
     <row r="8" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>51</v>
+        <v>71</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>61</v>
+        <v>81</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>49</v>
+        <v>69</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="J8" s="7" t="s">
-        <v>62</v>
+        <v>82</v>
       </c>
     </row>
     <row r="9" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>51</v>
+        <v>71</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>63</v>
+        <v>83</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>49</v>
+        <v>69</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="J9" s="7" t="s">
-        <v>64</v>
+        <v>84</v>
       </c>
     </row>
     <row r="10" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>51</v>
+        <v>71</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>49</v>
+        <v>69</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="J10" s="7" t="s">
-        <v>66</v>
+        <v>86</v>
       </c>
     </row>
     <row r="11" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>51</v>
+        <v>71</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>67</v>
+        <v>87</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>49</v>
+        <v>69</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="J11" s="7" t="s">
-        <v>68</v>
+        <v>88</v>
       </c>
     </row>
     <row r="12" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="B12" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="F12" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="C12" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>72</v>
-      </c>
       <c r="G12" s="6" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="J12" s="7" t="s">
-        <v>73</v>
+        <v>92</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:J1"/>
-  <dataValidations count="4">
+  <dataValidations count="5">
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="G10:G11">
       <formula1>Listas!$C$2:$C$9</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="G12">
+      <formula1>Listas!$D$2:$D$21</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="G2">
       <formula1>Listas!$A$2:$A$3</formula1>
@@ -1623,766 +1749,766 @@
   <sheetData>
     <row r="1" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>29</v>
+        <v>49</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>74</v>
+        <v>93</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>75</v>
+        <v>94</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>76</v>
+        <v>95</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>77</v>
+        <v>96</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>36</v>
+        <v>56</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>37</v>
+        <v>57</v>
       </c>
     </row>
     <row r="2" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>78</v>
+        <v>97</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>80</v>
+        <v>27</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>81</v>
+        <v>98</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="I2" s="7" t="s">
-        <v>82</v>
+        <v>99</v>
       </c>
     </row>
     <row r="3" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>83</v>
+        <v>100</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>84</v>
+        <v>101</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>86</v>
+        <v>103</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>87</v>
+        <v>104</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="I3" s="7" t="s">
-        <v>88</v>
+        <v>105</v>
       </c>
     </row>
     <row r="4" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>89</v>
+        <v>106</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>80</v>
+        <v>27</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>81</v>
+        <v>98</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="I4" s="7" t="s">
-        <v>90</v>
+        <v>107</v>
       </c>
     </row>
     <row r="5" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>91</v>
+        <v>108</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>47</v>
+        <v>67</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>92</v>
+        <v>109</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>93</v>
+        <v>110</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>94</v>
+        <v>111</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="I5" s="7" t="s">
-        <v>95</v>
+        <v>112</v>
       </c>
     </row>
     <row r="6" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>96</v>
+        <v>113</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>97</v>
+        <v>39</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>98</v>
+        <v>114</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="I6" s="7" t="s">
-        <v>99</v>
+        <v>115</v>
       </c>
     </row>
     <row r="7" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>100</v>
+        <v>116</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>80</v>
+        <v>27</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>81</v>
+        <v>98</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="I7" s="7" t="s">
-        <v>101</v>
+        <v>117</v>
       </c>
     </row>
     <row r="8" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>102</v>
+        <v>118</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>103</v>
+        <v>35</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>104</v>
+        <v>119</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="I8" s="7" t="s">
-        <v>105</v>
+        <v>120</v>
       </c>
     </row>
     <row r="9" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>106</v>
+        <v>121</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>47</v>
+        <v>67</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>92</v>
+        <v>109</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>107</v>
+        <v>122</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>94</v>
+        <v>111</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="I9" s="7" t="s">
-        <v>108</v>
+        <v>123</v>
       </c>
     </row>
     <row r="10" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>109</v>
+        <v>124</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>103</v>
+        <v>35</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>104</v>
+        <v>119</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="I10" s="7" t="s">
-        <v>110</v>
+        <v>125</v>
       </c>
     </row>
     <row r="11" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>111</v>
+        <v>126</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>47</v>
+        <v>67</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>92</v>
+        <v>109</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>15</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>94</v>
+        <v>111</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="I11" s="7" t="s">
-        <v>112</v>
+        <v>127</v>
       </c>
     </row>
     <row r="12" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>113</v>
+        <v>128</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>103</v>
+        <v>35</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>104</v>
+        <v>119</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="I12" s="7" t="s">
-        <v>114</v>
+        <v>129</v>
       </c>
     </row>
     <row r="13" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>115</v>
+        <v>130</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>103</v>
+        <v>35</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>104</v>
+        <v>119</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="I13" s="7" t="s">
-        <v>116</v>
+        <v>131</v>
       </c>
     </row>
     <row r="14" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>117</v>
+        <v>132</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>103</v>
+        <v>35</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>104</v>
+        <v>119</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="I14" s="7" t="s">
-        <v>118</v>
+        <v>133</v>
       </c>
     </row>
     <row r="15" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>119</v>
+        <v>134</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>120</v>
+        <v>135</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>121</v>
+        <v>136</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>122</v>
+        <v>137</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>123</v>
+        <v>138</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="I15" s="7" t="s">
-        <v>124</v>
+        <v>139</v>
       </c>
     </row>
     <row r="16" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>125</v>
+        <v>140</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>103</v>
+        <v>35</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>104</v>
+        <v>119</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="I16" s="7" t="s">
-        <v>126</v>
+        <v>141</v>
       </c>
     </row>
     <row r="17" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>127</v>
+        <v>142</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>120</v>
+        <v>135</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>121</v>
+        <v>136</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>122</v>
+        <v>137</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>123</v>
+        <v>138</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="I17" s="7" t="s">
-        <v>128</v>
+        <v>143</v>
       </c>
     </row>
     <row r="18" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>129</v>
+        <v>144</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>103</v>
+        <v>35</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>104</v>
+        <v>119</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="I18" s="7" t="s">
-        <v>130</v>
+        <v>145</v>
       </c>
     </row>
     <row r="19" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>131</v>
+        <v>146</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>47</v>
+        <v>67</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>92</v>
+        <v>109</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>132</v>
+        <v>147</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>94</v>
+        <v>111</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="I19" s="7" t="s">
-        <v>133</v>
+        <v>148</v>
       </c>
     </row>
     <row r="20" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>134</v>
+        <v>149</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>135</v>
+        <v>31</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>136</v>
+        <v>150</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="I20" s="7" t="s">
-        <v>137</v>
+        <v>151</v>
       </c>
     </row>
     <row r="21" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>69</v>
+        <v>89</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>92</v>
+        <v>136</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>138</v>
+        <v>152</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>139</v>
+        <v>153</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="H21" s="6" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="I21" s="7" t="s">
-        <v>140</v>
+        <v>154</v>
       </c>
     </row>
     <row r="22" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>141</v>
+        <v>155</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>142</v>
+        <v>33</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>143</v>
+        <v>156</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="I22" s="7" t="s">
-        <v>144</v>
+        <v>157</v>
       </c>
     </row>
     <row r="23" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>145</v>
+        <v>158</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>142</v>
+        <v>33</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>143</v>
+        <v>156</v>
       </c>
       <c r="F23" s="6" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="G23" s="6" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="H23" s="6" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="I23" s="7" t="s">
-        <v>146</v>
+        <v>159</v>
       </c>
     </row>
     <row r="24" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>147</v>
+        <v>160</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>148</v>
+        <v>43</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>149</v>
+        <v>161</v>
       </c>
       <c r="F24" s="6" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="I24" s="7" t="s">
-        <v>150</v>
+        <v>162</v>
       </c>
     </row>
     <row r="25" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>151</v>
+        <v>163</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>103</v>
+        <v>35</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>104</v>
+        <v>119</v>
       </c>
       <c r="F25" s="6" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="G25" s="6" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="H25" s="6" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="I25" s="7" t="s">
-        <v>152</v>
+        <v>164</v>
       </c>
     </row>
     <row r="26" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>135</v>
+        <v>31</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>136</v>
+        <v>150</v>
       </c>
       <c r="F26" s="6" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="I26" s="7" t="s">
-        <v>153</v>
+        <v>165</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:I1"/>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="F10:F26">
-      <formula1>Listas!$D$2:$D$3</formula1>
+      <formula1>Listas!$E$2:$E$3</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="F2:F26">
-      <formula1>Listas!$D$2:$D$3</formula1>
+      <formula1>Listas!$E$2:$E$3</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2409,34 +2535,34 @@
   <sheetData>
     <row r="1" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>29</v>
+        <v>49</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>154</v>
+        <v>166</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>156</v>
+        <v>168</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>158</v>
+        <v>170</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>76</v>
+        <v>95</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>36</v>
+        <v>56</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>37</v>
+        <v>57</v>
       </c>
     </row>
   </sheetData>
@@ -2466,37 +2592,37 @@
   <sheetData>
     <row r="1" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>29</v>
+        <v>49</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>160</v>
+        <v>172</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>75</v>
+        <v>94</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>161</v>
+        <v>173</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>162</v>
+        <v>174</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>163</v>
+        <v>175</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>164</v>
+        <v>176</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="K1" s="5" t="s">
-        <v>165</v>
+        <v>177</v>
       </c>
     </row>
     <row r="2" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2504,34 +2630,34 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>78</v>
+        <v>97</v>
       </c>
       <c r="C2" s="3">
         <v>114</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>81</v>
+        <v>98</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>166</v>
+        <v>178</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>167</v>
+        <v>179</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>168</v>
+        <v>180</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>168</v>
+        <v>180</v>
       </c>
       <c r="I2" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>169</v>
+        <v>181</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>170</v>
+        <v>182</v>
       </c>
     </row>
     <row r="3" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2539,34 +2665,34 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>83</v>
+        <v>100</v>
       </c>
       <c r="C3" s="3">
         <v>126</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>87</v>
+        <v>104</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>171</v>
+        <v>183</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>172</v>
+        <v>184</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>168</v>
+        <v>180</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>168</v>
+        <v>180</v>
       </c>
       <c r="I3" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>169</v>
+        <v>181</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>173</v>
+        <v>185</v>
       </c>
     </row>
     <row r="4" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2574,34 +2700,34 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>89</v>
+        <v>106</v>
       </c>
       <c r="C4" s="3">
         <v>52</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>81</v>
+        <v>98</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>166</v>
+        <v>178</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>167</v>
+        <v>179</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>168</v>
+        <v>180</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>168</v>
+        <v>180</v>
       </c>
       <c r="I4" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>169</v>
+        <v>181</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>170</v>
+        <v>182</v>
       </c>
     </row>
     <row r="5" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2609,34 +2735,34 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>91</v>
+        <v>108</v>
       </c>
       <c r="C5" s="3">
         <v>72</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>94</v>
+        <v>111</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>174</v>
+        <v>186</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>175</v>
+        <v>187</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>168</v>
+        <v>180</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>168</v>
+        <v>180</v>
       </c>
       <c r="I5" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>176</v>
+        <v>188</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>173</v>
+        <v>185</v>
       </c>
     </row>
     <row r="6" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2644,34 +2770,34 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>96</v>
+        <v>113</v>
       </c>
       <c r="C6" s="3">
         <v>452</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>98</v>
+        <v>114</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>166</v>
+        <v>178</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>167</v>
+        <v>179</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>168</v>
+        <v>180</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>168</v>
+        <v>180</v>
       </c>
       <c r="I6" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>169</v>
+        <v>181</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>170</v>
+        <v>182</v>
       </c>
     </row>
     <row r="7" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2679,34 +2805,34 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>100</v>
+        <v>116</v>
       </c>
       <c r="C7" s="3">
         <v>178</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>81</v>
+        <v>98</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>166</v>
+        <v>178</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>167</v>
+        <v>179</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>168</v>
+        <v>180</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>168</v>
+        <v>180</v>
       </c>
       <c r="I7" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>169</v>
+        <v>181</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>170</v>
+        <v>182</v>
       </c>
     </row>
     <row r="8" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2714,34 +2840,34 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>102</v>
+        <v>118</v>
       </c>
       <c r="C8" s="3">
         <v>82</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>104</v>
+        <v>119</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>166</v>
+        <v>178</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>167</v>
+        <v>179</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>168</v>
+        <v>180</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>168</v>
+        <v>180</v>
       </c>
       <c r="I8" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>169</v>
+        <v>181</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>170</v>
+        <v>182</v>
       </c>
     </row>
     <row r="9" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2749,34 +2875,34 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>106</v>
+        <v>121</v>
       </c>
       <c r="C9" s="3">
         <v>180</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>94</v>
+        <v>111</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>174</v>
+        <v>186</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>175</v>
+        <v>187</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>168</v>
+        <v>180</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>168</v>
+        <v>180</v>
       </c>
       <c r="I9" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>177</v>
+        <v>189</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>173</v>
+        <v>185</v>
       </c>
     </row>
     <row r="10" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2784,34 +2910,34 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>109</v>
+        <v>124</v>
       </c>
       <c r="C10" s="3">
         <v>44</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>104</v>
+        <v>119</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>166</v>
+        <v>178</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>167</v>
+        <v>179</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>168</v>
+        <v>180</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>168</v>
+        <v>180</v>
       </c>
       <c r="I10" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>169</v>
+        <v>181</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>170</v>
+        <v>182</v>
       </c>
     </row>
     <row r="11" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2819,34 +2945,34 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>111</v>
+        <v>126</v>
       </c>
       <c r="C11" s="3">
         <v>4</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>94</v>
+        <v>111</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>174</v>
+        <v>186</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>175</v>
+        <v>187</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>168</v>
+        <v>180</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>168</v>
+        <v>180</v>
       </c>
       <c r="I11" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>169</v>
+        <v>181</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>173</v>
+        <v>185</v>
       </c>
     </row>
     <row r="12" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2854,34 +2980,34 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>113</v>
+        <v>128</v>
       </c>
       <c r="C12" s="3">
         <v>18</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>104</v>
+        <v>119</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>166</v>
+        <v>178</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>167</v>
+        <v>179</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>168</v>
+        <v>180</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>168</v>
+        <v>180</v>
       </c>
       <c r="I12" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>169</v>
+        <v>181</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>170</v>
+        <v>182</v>
       </c>
     </row>
     <row r="13" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2889,34 +3015,34 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="C13" s="3">
         <v>4</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>174</v>
+        <v>186</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>175</v>
+        <v>187</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>168</v>
+        <v>180</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>168</v>
+        <v>180</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>168</v>
+        <v>180</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>173</v>
+        <v>185</v>
       </c>
     </row>
     <row r="14" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2924,34 +3050,34 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>115</v>
+        <v>130</v>
       </c>
       <c r="C14" s="3">
         <v>2</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>104</v>
+        <v>119</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>166</v>
+        <v>178</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>167</v>
+        <v>179</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>168</v>
+        <v>180</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>168</v>
+        <v>180</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>169</v>
+        <v>181</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>170</v>
+        <v>182</v>
       </c>
     </row>
     <row r="15" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2959,34 +3085,34 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>51</v>
+        <v>71</v>
       </c>
       <c r="C15" s="3">
         <v>40</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>182</v>
+        <v>194</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>168</v>
+        <v>180</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>168</v>
+        <v>180</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>168</v>
+        <v>180</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>173</v>
+        <v>185</v>
       </c>
     </row>
     <row r="16" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2994,34 +3120,34 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>117</v>
+        <v>132</v>
       </c>
       <c r="C16" s="3">
         <v>70</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>104</v>
+        <v>119</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>166</v>
+        <v>178</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>167</v>
+        <v>179</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>168</v>
+        <v>180</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>168</v>
+        <v>180</v>
       </c>
       <c r="I16" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>169</v>
+        <v>181</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>170</v>
+        <v>182</v>
       </c>
     </row>
     <row r="17" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3029,34 +3155,34 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>119</v>
+        <v>134</v>
       </c>
       <c r="C17" s="3">
         <v>14</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>123</v>
+        <v>138</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>183</v>
+        <v>195</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>184</v>
+        <v>196</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>168</v>
+        <v>180</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>168</v>
+        <v>180</v>
       </c>
       <c r="I17" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J17" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="K17" s="3" t="s">
         <v>185</v>
-      </c>
-      <c r="K17" s="3" t="s">
-        <v>173</v>
       </c>
     </row>
     <row r="18" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3064,34 +3190,34 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>125</v>
+        <v>140</v>
       </c>
       <c r="C18" s="3">
         <v>2</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>104</v>
+        <v>119</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>166</v>
+        <v>178</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>167</v>
+        <v>179</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>168</v>
+        <v>180</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>168</v>
+        <v>180</v>
       </c>
       <c r="I18" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>169</v>
+        <v>181</v>
       </c>
       <c r="K18" s="3" t="s">
-        <v>170</v>
+        <v>182</v>
       </c>
     </row>
     <row r="19" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3099,34 +3225,34 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>127</v>
+        <v>142</v>
       </c>
       <c r="C19" s="3">
         <v>14</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>123</v>
+        <v>138</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>183</v>
+        <v>195</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>184</v>
+        <v>196</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>168</v>
+        <v>180</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>168</v>
+        <v>180</v>
       </c>
       <c r="I19" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J19" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="K19" s="3" t="s">
         <v>185</v>
-      </c>
-      <c r="K19" s="3" t="s">
-        <v>173</v>
       </c>
     </row>
     <row r="20" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3134,34 +3260,34 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>129</v>
+        <v>144</v>
       </c>
       <c r="C20" s="3">
         <v>86</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>104</v>
+        <v>119</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>166</v>
+        <v>178</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>167</v>
+        <v>179</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>168</v>
+        <v>180</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>168</v>
+        <v>180</v>
       </c>
       <c r="I20" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>169</v>
+        <v>181</v>
       </c>
       <c r="K20" s="3" t="s">
-        <v>170</v>
+        <v>182</v>
       </c>
     </row>
     <row r="21" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3169,34 +3295,34 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>131</v>
+        <v>146</v>
       </c>
       <c r="C21" s="3">
         <v>80</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>94</v>
+        <v>111</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>174</v>
+        <v>186</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>175</v>
+        <v>187</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>168</v>
+        <v>180</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>168</v>
+        <v>180</v>
       </c>
       <c r="I21" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>186</v>
+        <v>198</v>
       </c>
       <c r="K21" s="3" t="s">
-        <v>173</v>
+        <v>185</v>
       </c>
     </row>
     <row r="22" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3204,34 +3330,34 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>134</v>
+        <v>149</v>
       </c>
       <c r="C22" s="3">
         <v>252</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>136</v>
+        <v>150</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>166</v>
+        <v>178</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>167</v>
+        <v>179</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>168</v>
+        <v>180</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>168</v>
+        <v>180</v>
       </c>
       <c r="I22" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>169</v>
+        <v>181</v>
       </c>
       <c r="K22" s="3" t="s">
-        <v>170</v>
+        <v>182</v>
       </c>
     </row>
     <row r="23" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3239,34 +3365,34 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>69</v>
+        <v>89</v>
       </c>
       <c r="C23" s="3">
         <v>2</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>139</v>
+        <v>153</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>187</v>
+        <v>199</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>188</v>
+        <v>200</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>168</v>
+        <v>180</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>168</v>
+        <v>180</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>189</v>
+        <v>201</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>169</v>
+        <v>197</v>
       </c>
       <c r="K23" s="3" t="s">
-        <v>173</v>
+        <v>185</v>
       </c>
     </row>
     <row r="24" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3274,34 +3400,34 @@
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>141</v>
+        <v>155</v>
       </c>
       <c r="C24" s="3">
         <v>142</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>143</v>
+        <v>156</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>166</v>
+        <v>178</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>167</v>
+        <v>179</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>168</v>
+        <v>180</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>168</v>
+        <v>180</v>
       </c>
       <c r="I24" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>169</v>
+        <v>181</v>
       </c>
       <c r="K24" s="3" t="s">
-        <v>170</v>
+        <v>182</v>
       </c>
     </row>
     <row r="25" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3309,34 +3435,34 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>190</v>
+        <v>202</v>
       </c>
       <c r="C25" s="3">
         <v>110</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>191</v>
+        <v>203</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>192</v>
+        <v>204</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>193</v>
+        <v>205</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>168</v>
+        <v>180</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>168</v>
+        <v>180</v>
       </c>
       <c r="I25" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>168</v>
+        <v>180</v>
       </c>
       <c r="K25" s="3" t="s">
-        <v>173</v>
+        <v>185</v>
       </c>
     </row>
     <row r="26" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3344,34 +3470,34 @@
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>145</v>
+        <v>158</v>
       </c>
       <c r="C26" s="3">
         <v>176</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>143</v>
+        <v>156</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>166</v>
+        <v>178</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>167</v>
+        <v>179</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>168</v>
+        <v>180</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>168</v>
+        <v>180</v>
       </c>
       <c r="I26" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>169</v>
+        <v>181</v>
       </c>
       <c r="K26" s="3" t="s">
-        <v>170</v>
+        <v>182</v>
       </c>
     </row>
     <row r="27" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3379,34 +3505,34 @@
         <v>26</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>147</v>
+        <v>160</v>
       </c>
       <c r="C27" s="3">
         <v>120</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>149</v>
+        <v>161</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>166</v>
+        <v>178</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>167</v>
+        <v>179</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>168</v>
+        <v>180</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>168</v>
+        <v>180</v>
       </c>
       <c r="I27" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>169</v>
+        <v>181</v>
       </c>
       <c r="K27" s="3" t="s">
-        <v>170</v>
+        <v>182</v>
       </c>
     </row>
     <row r="28" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3414,34 +3540,34 @@
         <v>27</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>151</v>
+        <v>163</v>
       </c>
       <c r="C28" s="3">
         <v>468</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>104</v>
+        <v>119</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>166</v>
+        <v>178</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>167</v>
+        <v>179</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>168</v>
+        <v>180</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>168</v>
+        <v>180</v>
       </c>
       <c r="I28" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>169</v>
+        <v>181</v>
       </c>
       <c r="K28" s="3" t="s">
-        <v>170</v>
+        <v>182</v>
       </c>
     </row>
     <row r="29" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3449,34 +3575,34 @@
         <v>28</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="C29" s="3">
         <v>189</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>136</v>
+        <v>150</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>166</v>
+        <v>178</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>167</v>
+        <v>179</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>168</v>
+        <v>180</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>168</v>
+        <v>180</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>194</v>
+        <v>206</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>169</v>
+        <v>181</v>
       </c>
       <c r="K29" s="3" t="s">
-        <v>170</v>
+        <v>182</v>
       </c>
     </row>
   </sheetData>

--- a/docs/dominio-metrico/migracion/cuestionarios/el-conde-de-sex.xlsx
+++ b/docs/dominio-metrico/migracion/cuestionarios/el-conde-de-sex.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="679" uniqueCount="207">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="648" uniqueCount="191">
   <si>
     <t>Migración métrica · El conde de Sex</t>
   </si>
@@ -69,9 +69,6 @@
     <t>Tipología 1 · ababa</t>
   </si>
   <si>
-    <t>a</t>
-  </si>
-  <si>
     <t>Es correcto</t>
   </si>
   <si>
@@ -84,423 +81,381 @@
     <t>Tipología 2 · abbab</t>
   </si>
   <si>
-    <t>a-a</t>
-  </si>
-  <si>
     <t>No es así (lo corrijo al lado)</t>
   </si>
   <si>
     <t>Tipología 3 · abaab</t>
   </si>
   <si>
-    <t>a-e</t>
-  </si>
-  <si>
     <t>Tipología 4 · aabab</t>
   </si>
   <si>
+    <t>Tipología 5 · aabba</t>
+  </si>
+  <si>
+    <t>Tipología 6 · abbaa</t>
+  </si>
+  <si>
+    <t>Tipología 7 · ababb</t>
+  </si>
+  <si>
+    <t>Tipología 8 · abbba</t>
+  </si>
+  <si>
+    <t>Tipo</t>
+  </si>
+  <si>
+    <t>Versos</t>
+  </si>
+  <si>
+    <t>Forma</t>
+  </si>
+  <si>
+    <t>Qué se pregunta</t>
+  </si>
+  <si>
+    <t>Propuesta</t>
+  </si>
+  <si>
+    <t>Cómo contestar</t>
+  </si>
+  <si>
+    <t>Respuesta</t>
+  </si>
+  <si>
+    <t>Excepciones / detalle</t>
+  </si>
+  <si>
+    <t>Comentario</t>
+  </si>
+  <si>
+    <t>Clave</t>
+  </si>
+  <si>
+    <t>Decidir</t>
+  </si>
+  <si>
+    <t>2905–3093</t>
+  </si>
+  <si>
+    <t>Romance · Octosílabo</t>
+  </si>
+  <si>
+    <t>Tiene 189 versos, y un romance octosílabo no puede tener un número impar: en algún punto falta o sobra un verso. Hay que localizarlo y decir si se trata de una laguna, en cuyo caso renumeraré la obra a partir de ahí, o de un error en el rango, en cuyo caso hace falta el rango correcto. Las preguntas que dependen de cómo se reparta en estrofas te las haré cuando esto esté claro.</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Elige en el desplegable y explícalo al lado</t>
+  </si>
+  <si>
+    <t>L|ecce2c2a-1692-41a3-9788-d9f498297c03</t>
+  </si>
+  <si>
+    <t>Responder</t>
+  </si>
+  <si>
+    <t>1323–1326</t>
+  </si>
+  <si>
+    <t>Redondilla · Octosílaba</t>
+  </si>
+  <si>
+    <t>Esquema de rima · 1 estrofa</t>
+  </si>
+  <si>
+    <t>Elige en el desplegable</t>
+  </si>
+  <si>
+    <t>R|aee2cdd0-525a-4512-8320-07939a7a627c|b4bad32a-b9ac-4304-9003-e8af28ecc3f0</t>
+  </si>
+  <si>
+    <t>1329–1368</t>
+  </si>
+  <si>
+    <t>Quintilla · Octosílaba consonante</t>
+  </si>
+  <si>
+    <t>Esquema de rima · estrofa 1 (vv. 1329–1333)</t>
+  </si>
+  <si>
+    <t>U|0cbaa6dc-b3e1-4f2b-bba6-1317c0a9c141|a43860ff-566c-4a0b-b210-4572b8d7b066|1329</t>
+  </si>
+  <si>
+    <t>Esquema de rima · estrofa 2 (vv. 1334–1338)</t>
+  </si>
+  <si>
+    <t>U|0cbaa6dc-b3e1-4f2b-bba6-1317c0a9c141|a43860ff-566c-4a0b-b210-4572b8d7b066|1334</t>
+  </si>
+  <si>
+    <t>Esquema de rima · estrofa 3 (vv. 1339–1343)</t>
+  </si>
+  <si>
+    <t>U|0cbaa6dc-b3e1-4f2b-bba6-1317c0a9c141|a43860ff-566c-4a0b-b210-4572b8d7b066|1339</t>
+  </si>
+  <si>
+    <t>Esquema de rima · estrofa 4 (vv. 1344–1348)</t>
+  </si>
+  <si>
+    <t>U|0cbaa6dc-b3e1-4f2b-bba6-1317c0a9c141|a43860ff-566c-4a0b-b210-4572b8d7b066|1344</t>
+  </si>
+  <si>
+    <t>Esquema de rima · estrofa 5 (vv. 1349–1353)</t>
+  </si>
+  <si>
+    <t>U|0cbaa6dc-b3e1-4f2b-bba6-1317c0a9c141|a43860ff-566c-4a0b-b210-4572b8d7b066|1349</t>
+  </si>
+  <si>
+    <t>Esquema de rima · estrofa 6 (vv. 1354–1358)</t>
+  </si>
+  <si>
+    <t>U|0cbaa6dc-b3e1-4f2b-bba6-1317c0a9c141|a43860ff-566c-4a0b-b210-4572b8d7b066|1354</t>
+  </si>
+  <si>
+    <t>Esquema de rima · estrofa 7 (vv. 1359–1363)</t>
+  </si>
+  <si>
+    <t>U|0cbaa6dc-b3e1-4f2b-bba6-1317c0a9c141|a43860ff-566c-4a0b-b210-4572b8d7b066|1359</t>
+  </si>
+  <si>
+    <t>Esquema de rima · estrofa 8 (vv. 1364–1368)</t>
+  </si>
+  <si>
+    <t>U|0cbaa6dc-b3e1-4f2b-bba6-1317c0a9c141|a43860ff-566c-4a0b-b210-4572b8d7b066|1364</t>
+  </si>
+  <si>
+    <t>Pregunta</t>
+  </si>
+  <si>
+    <t>Vocabulario anterior</t>
+  </si>
+  <si>
+    <t>¿Correcto?</t>
+  </si>
+  <si>
+    <t>Corrección</t>
+  </si>
+  <si>
+    <t>1–114</t>
+  </si>
+  <si>
+    <t>Vocales de la asonancia</t>
+  </si>
+  <si>
     <t>a-o</t>
   </si>
   <si>
-    <t>Tipología 5 · aabba</t>
-  </si>
-  <si>
-    <t>e</t>
-  </si>
-  <si>
-    <t>Tipología 6 · abbaa</t>
+    <t>romance_a-o</t>
+  </si>
+  <si>
+    <t>C|990ab180-f289-4d6a-86d1-e19aa334a3bc</t>
+  </si>
+  <si>
+    <t>115–240</t>
+  </si>
+  <si>
+    <t>Silva · Consonante de orden libre</t>
+  </si>
+  <si>
+    <t>Densidad de rima</t>
+  </si>
+  <si>
+    <t>Mayoritaria</t>
+  </si>
+  <si>
+    <t>silva_de_consonantes_irregular</t>
+  </si>
+  <si>
+    <t>C|a9633596-d00f-4951-9296-5543d5f42dd5</t>
+  </si>
+  <si>
+    <t>241–292</t>
+  </si>
+  <si>
+    <t>C|5a24100c-d8f8-4de8-b3b0-76eb722533c9</t>
+  </si>
+  <si>
+    <t>293–364</t>
+  </si>
+  <si>
+    <t>Esquema de rima</t>
+  </si>
+  <si>
+    <t>Abrazada · abba en las 18 estrofas</t>
+  </si>
+  <si>
+    <t>redondilla_regular</t>
+  </si>
+  <si>
+    <t>C|547d3f23-b238-4d36-b033-e07563c33781</t>
+  </si>
+  <si>
+    <t>365–816</t>
+  </si>
+  <si>
+    <t>i-o</t>
+  </si>
+  <si>
+    <t>romance_i-o</t>
+  </si>
+  <si>
+    <t>C|eb90aef7-fc5f-411f-a9c5-eafccde6abfc</t>
+  </si>
+  <si>
+    <t>817–994</t>
+  </si>
+  <si>
+    <t>C|5ae8ba04-f93e-4f90-a2ac-af2e5d607d43</t>
+  </si>
+  <si>
+    <t>995–1076</t>
+  </si>
+  <si>
+    <t>e-o</t>
+  </si>
+  <si>
+    <t>romance_e-o</t>
+  </si>
+  <si>
+    <t>C|ed8ce141-f4fe-4ea5-9ced-557cc1557b76</t>
+  </si>
+  <si>
+    <t>1077–1256</t>
+  </si>
+  <si>
+    <t>Abrazada · abba en las 45 estrofas</t>
+  </si>
+  <si>
+    <t>C|99d15682-ecac-45d9-a544-6a57cf0846e8</t>
+  </si>
+  <si>
+    <t>1257–1300</t>
+  </si>
+  <si>
+    <t>C|6e93f9aa-083e-4b4a-a6fd-ef0fd28306d4</t>
+  </si>
+  <si>
+    <t>1301–1304</t>
+  </si>
+  <si>
+    <t>C|8f2934ab-8a1c-4548-b5be-2c03ac18558b</t>
+  </si>
+  <si>
+    <t>1305–1322</t>
+  </si>
+  <si>
+    <t>C|20ce6ede-c2bf-4083-bbd7-680b2a309f41</t>
+  </si>
+  <si>
+    <t>1327–1328</t>
+  </si>
+  <si>
+    <t>C|f1a18594-6f0b-411c-8d79-9374c3da9239</t>
+  </si>
+  <si>
+    <t>1369–1438</t>
+  </si>
+  <si>
+    <t>C|9b9e4d9c-b1c8-4849-8f0c-6eb696c495a1</t>
+  </si>
+  <si>
+    <t>1439–1452</t>
+  </si>
+  <si>
+    <t>Soneto · Endecasílabo consonante</t>
+  </si>
+  <si>
+    <t>Varias respuestas</t>
+  </si>
+  <si>
+    <t>Cuartetos · Esquema de rima: Cuartetos de rima abrazada · ABBA ABBA; Tercetos · Esquema de rima: Tercetos de rima cruzada · CDC DCD</t>
+  </si>
+  <si>
+    <t>soneto_regular_ABBAABBACDCDCD</t>
+  </si>
+  <si>
+    <t>C|1fb56175-bdc4-4f4f-943e-028061a1b32f</t>
+  </si>
+  <si>
+    <t>1453–1454</t>
+  </si>
+  <si>
+    <t>C|2da15d83-ab9b-4bb1-a65e-727494bd9ae8</t>
+  </si>
+  <si>
+    <t>1455–1468</t>
+  </si>
+  <si>
+    <t>C|8fb46735-a928-4a3b-a933-945bb26c065d</t>
+  </si>
+  <si>
+    <t>1469–1554</t>
+  </si>
+  <si>
+    <t>C|22fd2bf5-9560-44c5-bc74-40b3c5b296a7</t>
+  </si>
+  <si>
+    <t>1555–1634</t>
+  </si>
+  <si>
+    <t>Abrazada · abba en las 20 estrofas</t>
+  </si>
+  <si>
+    <t>C|8a65f4f1-fa90-4b25-880b-b41acc9782d0</t>
+  </si>
+  <si>
+    <t>1635–1886</t>
   </si>
   <si>
     <t>e-a</t>
   </si>
   <si>
-    <t>Tipología 7 · ababb</t>
+    <t>romance_e-a</t>
+  </si>
+  <si>
+    <t>C|7d55b05a-6034-4056-9d8d-8c741592e584</t>
+  </si>
+  <si>
+    <t>1887–1888</t>
+  </si>
+  <si>
+    <t>Pareado · Isométrico</t>
+  </si>
+  <si>
+    <t>Esquema de rima: aa · Consonante; Medida de los versos: Endecasílabo</t>
+  </si>
+  <si>
+    <t>pareado_endecasilabo</t>
+  </si>
+  <si>
+    <t>C|cb94c0f3-5ba7-49e7-a0ea-ba1ca41f070a</t>
+  </si>
+  <si>
+    <t>1889–2030</t>
   </si>
   <si>
     <t>e-e</t>
   </si>
   <si>
-    <t>Tipología 8 · abbba</t>
-  </si>
-  <si>
-    <t>e-o</t>
-  </si>
-  <si>
-    <t>i</t>
-  </si>
-  <si>
-    <t>i-a</t>
-  </si>
-  <si>
-    <t>i-e</t>
-  </si>
-  <si>
-    <t>i-o</t>
-  </si>
-  <si>
-    <t>o</t>
-  </si>
-  <si>
-    <t>o-a</t>
-  </si>
-  <si>
-    <t>o-e</t>
+    <t>romance_e-e</t>
+  </si>
+  <si>
+    <t>C|160f34b0-9e22-41b5-9e6c-8fc00f0f5001</t>
+  </si>
+  <si>
+    <t>2141–2316</t>
+  </si>
+  <si>
+    <t>C|5aa7201b-6a07-401f-a08a-b4be0676f2b8</t>
+  </si>
+  <si>
+    <t>2317–2436</t>
   </si>
   <si>
     <t>o-o</t>
   </si>
   <si>
-    <t>u</t>
-  </si>
-  <si>
-    <t>u-a</t>
-  </si>
-  <si>
-    <t>u-e</t>
-  </si>
-  <si>
-    <t>u-o</t>
-  </si>
-  <si>
-    <t>Tipo</t>
-  </si>
-  <si>
-    <t>Versos</t>
-  </si>
-  <si>
-    <t>Forma</t>
-  </si>
-  <si>
-    <t>Qué se pregunta</t>
-  </si>
-  <si>
-    <t>Propuesta</t>
-  </si>
-  <si>
-    <t>Cómo contestar</t>
-  </si>
-  <si>
-    <t>Respuesta</t>
-  </si>
-  <si>
-    <t>Excepciones / detalle</t>
-  </si>
-  <si>
-    <t>Comentario</t>
-  </si>
-  <si>
-    <t>Clave</t>
-  </si>
-  <si>
-    <t>Decidir</t>
-  </si>
-  <si>
-    <t>2905–3093</t>
-  </si>
-  <si>
-    <t>Romance · Octosílabo</t>
-  </si>
-  <si>
-    <t>Tiene 189 versos, y un romance octosílabo no puede tener un número impar: en algún punto falta o sobra un verso. Hay que localizarlo y decir si se trata de una laguna, en cuyo caso renumeraré la obra a partir de ahí, o de un error en el rango, en cuyo caso hace falta el rango correcto. Las preguntas que dependen de cómo se reparta en estrofas te las haré cuando esto esté claro.</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>Elige en el desplegable y explícalo al lado</t>
-  </si>
-  <si>
-    <t>L|ecce2c2a-1692-41a3-9788-d9f498297c03</t>
-  </si>
-  <si>
-    <t>Responder</t>
-  </si>
-  <si>
-    <t>1323–1326</t>
-  </si>
-  <si>
-    <t>Redondilla · Octosílaba</t>
-  </si>
-  <si>
-    <t>Esquema de rima · 1 estrofa</t>
-  </si>
-  <si>
-    <t>Elige en el desplegable</t>
-  </si>
-  <si>
-    <t>R|aee2cdd0-525a-4512-8320-07939a7a627c|b4bad32a-b9ac-4304-9003-e8af28ecc3f0</t>
-  </si>
-  <si>
-    <t>1329–1368</t>
-  </si>
-  <si>
-    <t>Quintilla · Octosílaba consonante</t>
-  </si>
-  <si>
-    <t>Esquema de rima · estrofa 1 (vv. 1329–1333)</t>
-  </si>
-  <si>
-    <t>U|0cbaa6dc-b3e1-4f2b-bba6-1317c0a9c141|a43860ff-566c-4a0b-b210-4572b8d7b066|1329</t>
-  </si>
-  <si>
-    <t>Esquema de rima · estrofa 2 (vv. 1334–1338)</t>
-  </si>
-  <si>
-    <t>U|0cbaa6dc-b3e1-4f2b-bba6-1317c0a9c141|a43860ff-566c-4a0b-b210-4572b8d7b066|1334</t>
-  </si>
-  <si>
-    <t>Esquema de rima · estrofa 3 (vv. 1339–1343)</t>
-  </si>
-  <si>
-    <t>U|0cbaa6dc-b3e1-4f2b-bba6-1317c0a9c141|a43860ff-566c-4a0b-b210-4572b8d7b066|1339</t>
-  </si>
-  <si>
-    <t>Esquema de rima · estrofa 4 (vv. 1344–1348)</t>
-  </si>
-  <si>
-    <t>U|0cbaa6dc-b3e1-4f2b-bba6-1317c0a9c141|a43860ff-566c-4a0b-b210-4572b8d7b066|1344</t>
-  </si>
-  <si>
-    <t>Esquema de rima · estrofa 5 (vv. 1349–1353)</t>
-  </si>
-  <si>
-    <t>U|0cbaa6dc-b3e1-4f2b-bba6-1317c0a9c141|a43860ff-566c-4a0b-b210-4572b8d7b066|1349</t>
-  </si>
-  <si>
-    <t>Esquema de rima · estrofa 6 (vv. 1354–1358)</t>
-  </si>
-  <si>
-    <t>U|0cbaa6dc-b3e1-4f2b-bba6-1317c0a9c141|a43860ff-566c-4a0b-b210-4572b8d7b066|1354</t>
-  </si>
-  <si>
-    <t>Esquema de rima · estrofa 7 (vv. 1359–1363)</t>
-  </si>
-  <si>
-    <t>U|0cbaa6dc-b3e1-4f2b-bba6-1317c0a9c141|a43860ff-566c-4a0b-b210-4572b8d7b066|1359</t>
-  </si>
-  <si>
-    <t>Esquema de rima · estrofa 8 (vv. 1364–1368)</t>
-  </si>
-  <si>
-    <t>U|0cbaa6dc-b3e1-4f2b-bba6-1317c0a9c141|a43860ff-566c-4a0b-b210-4572b8d7b066|1364</t>
-  </si>
-  <si>
-    <t>1887–1888</t>
-  </si>
-  <si>
-    <t>Pareado · Isométrico</t>
-  </si>
-  <si>
-    <t>Vocales de la asonancia</t>
-  </si>
-  <si>
-    <t>R|cb94c0f3-5ba7-49e7-a0ea-ba1ca41f070a|da2e8262-3dbf-43d4-ba62-f492fa06dc8b</t>
-  </si>
-  <si>
-    <t>Pregunta</t>
-  </si>
-  <si>
-    <t>Vocabulario anterior</t>
-  </si>
-  <si>
-    <t>¿Correcto?</t>
-  </si>
-  <si>
-    <t>Corrección</t>
-  </si>
-  <si>
-    <t>1–114</t>
-  </si>
-  <si>
-    <t>romance_a-o</t>
-  </si>
-  <si>
-    <t>C|990ab180-f289-4d6a-86d1-e19aa334a3bc</t>
-  </si>
-  <si>
-    <t>115–240</t>
-  </si>
-  <si>
-    <t>Silva · Consonante de orden libre</t>
-  </si>
-  <si>
-    <t>Densidad de rima</t>
-  </si>
-  <si>
-    <t>Mayoritaria</t>
-  </si>
-  <si>
-    <t>silva_de_consonantes_irregular</t>
-  </si>
-  <si>
-    <t>C|a9633596-d00f-4951-9296-5543d5f42dd5</t>
-  </si>
-  <si>
-    <t>241–292</t>
-  </si>
-  <si>
-    <t>C|5a24100c-d8f8-4de8-b3b0-76eb722533c9</t>
-  </si>
-  <si>
-    <t>293–364</t>
-  </si>
-  <si>
-    <t>Esquema de rima</t>
-  </si>
-  <si>
-    <t>Abrazada · abba en las 18 estrofas</t>
-  </si>
-  <si>
-    <t>redondilla_regular</t>
-  </si>
-  <si>
-    <t>C|547d3f23-b238-4d36-b033-e07563c33781</t>
-  </si>
-  <si>
-    <t>365–816</t>
-  </si>
-  <si>
-    <t>romance_i-o</t>
-  </si>
-  <si>
-    <t>C|eb90aef7-fc5f-411f-a9c5-eafccde6abfc</t>
-  </si>
-  <si>
-    <t>817–994</t>
-  </si>
-  <si>
-    <t>C|5ae8ba04-f93e-4f90-a2ac-af2e5d607d43</t>
-  </si>
-  <si>
-    <t>995–1076</t>
-  </si>
-  <si>
-    <t>romance_e-o</t>
-  </si>
-  <si>
-    <t>C|ed8ce141-f4fe-4ea5-9ced-557cc1557b76</t>
-  </si>
-  <si>
-    <t>1077–1256</t>
-  </si>
-  <si>
-    <t>Abrazada · abba en las 45 estrofas</t>
-  </si>
-  <si>
-    <t>C|99d15682-ecac-45d9-a544-6a57cf0846e8</t>
-  </si>
-  <si>
-    <t>1257–1300</t>
-  </si>
-  <si>
-    <t>C|6e93f9aa-083e-4b4a-a6fd-ef0fd28306d4</t>
-  </si>
-  <si>
-    <t>1301–1304</t>
-  </si>
-  <si>
-    <t>C|8f2934ab-8a1c-4548-b5be-2c03ac18558b</t>
-  </si>
-  <si>
-    <t>1305–1322</t>
-  </si>
-  <si>
-    <t>C|20ce6ede-c2bf-4083-bbd7-680b2a309f41</t>
-  </si>
-  <si>
-    <t>1327–1328</t>
-  </si>
-  <si>
-    <t>C|f1a18594-6f0b-411c-8d79-9374c3da9239</t>
-  </si>
-  <si>
-    <t>1369–1438</t>
-  </si>
-  <si>
-    <t>C|9b9e4d9c-b1c8-4849-8f0c-6eb696c495a1</t>
-  </si>
-  <si>
-    <t>1439–1452</t>
-  </si>
-  <si>
-    <t>Soneto · Endecasílabo consonante</t>
-  </si>
-  <si>
-    <t>Varias respuestas</t>
-  </si>
-  <si>
-    <t>Cuartetos · Esquema de rima: Cuartetos de rima abrazada · ABBA ABBA; Tercetos · Esquema de rima: Tercetos de rima cruzada · CDC DCD</t>
-  </si>
-  <si>
-    <t>soneto_regular_ABBAABBACDCDCD</t>
-  </si>
-  <si>
-    <t>C|1fb56175-bdc4-4f4f-943e-028061a1b32f</t>
-  </si>
-  <si>
-    <t>1453–1454</t>
-  </si>
-  <si>
-    <t>C|2da15d83-ab9b-4bb1-a65e-727494bd9ae8</t>
-  </si>
-  <si>
-    <t>1455–1468</t>
-  </si>
-  <si>
-    <t>C|8fb46735-a928-4a3b-a933-945bb26c065d</t>
-  </si>
-  <si>
-    <t>1469–1554</t>
-  </si>
-  <si>
-    <t>C|22fd2bf5-9560-44c5-bc74-40b3c5b296a7</t>
-  </si>
-  <si>
-    <t>1555–1634</t>
-  </si>
-  <si>
-    <t>Abrazada · abba en las 20 estrofas</t>
-  </si>
-  <si>
-    <t>C|8a65f4f1-fa90-4b25-880b-b41acc9782d0</t>
-  </si>
-  <si>
-    <t>1635–1886</t>
-  </si>
-  <si>
-    <t>romance_e-a</t>
-  </si>
-  <si>
-    <t>C|7d55b05a-6034-4056-9d8d-8c741592e584</t>
-  </si>
-  <si>
-    <t>Esquema de rima: aa · Consonante; Medida de los versos: Endecasílabo</t>
-  </si>
-  <si>
-    <t>pareado_endecasilabo</t>
-  </si>
-  <si>
-    <t>C|cb94c0f3-5ba7-49e7-a0ea-ba1ca41f070a</t>
-  </si>
-  <si>
-    <t>1889–2030</t>
-  </si>
-  <si>
-    <t>romance_e-e</t>
-  </si>
-  <si>
-    <t>C|160f34b0-9e22-41b5-9e6c-8fc00f0f5001</t>
-  </si>
-  <si>
-    <t>2141–2316</t>
-  </si>
-  <si>
-    <t>C|5aa7201b-6a07-401f-a08a-b4be0676f2b8</t>
-  </si>
-  <si>
-    <t>2317–2436</t>
-  </si>
-  <si>
     <t>romance_o-o</t>
   </si>
   <si>
@@ -619,9 +574,6 @@
   </si>
   <si>
     <t>Isométrico</t>
-  </si>
-  <si>
-    <t>Falta: Vocales de la asonancia</t>
   </si>
   <si>
     <t>2031–2140</t>
@@ -1136,13 +1088,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="5" width="40" customWidth="1"/>
+    <col min="1" max="4" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>13</v>
       </c>
@@ -1155,11 +1107,8 @@
       <c r="D1" t="s">
         <v>13</v>
       </c>
-      <c r="E1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>14</v>
       </c>
@@ -1172,133 +1121,49 @@
       <c r="D2" t="s">
         <v>17</v>
       </c>
-      <c r="E2" t="s">
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="B3" t="s">
         <v>19</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>20</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>21</v>
       </c>
-      <c r="D3" t="s">
+    </row>
+    <row r="4" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C4" t="s">
         <v>22</v>
       </c>
-      <c r="E3" t="s">
+    </row>
+    <row r="5" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C5" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="4" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C4" t="s">
+    <row r="6" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C6" t="s">
         <v>24</v>
       </c>
-      <c r="D4" t="s">
+    </row>
+    <row r="7" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C7" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C5" t="s">
+    <row r="8" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C8" t="s">
         <v>26</v>
       </c>
-      <c r="D5" t="s">
+    </row>
+    <row r="9" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C9" t="s">
         <v>27</v>
-      </c>
-    </row>
-    <row r="6" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C6" t="s">
-        <v>28</v>
-      </c>
-      <c r="D6" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="7" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D7" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="8" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C8" t="s">
-        <v>32</v>
-      </c>
-      <c r="D8" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="9" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C9" t="s">
-        <v>34</v>
-      </c>
-      <c r="D9" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="10" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D10" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="11" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D11" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="12" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D12" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="13" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D13" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="14" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D14" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="15" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D15" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="16" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D16" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="17" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D17" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="18" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D18" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="19" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D19" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="20" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D20" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="21" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D21" t="s">
-        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -1309,7 +1174,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:J11"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="2" width="11" customWidth="1"/>
@@ -1325,396 +1190,361 @@
   <sheetData>
     <row r="1" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>56</v>
+        <v>36</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>57</v>
+        <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>59</v>
+        <v>39</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>61</v>
+        <v>41</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>63</v>
+        <v>43</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="J2" s="7" t="s">
-        <v>64</v>
+        <v>44</v>
       </c>
     </row>
     <row r="3" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>65</v>
+        <v>45</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>66</v>
+        <v>46</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>67</v>
+        <v>47</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>68</v>
+        <v>48</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="J3" s="7" t="s">
-        <v>70</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>65</v>
+        <v>45</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>73</v>
+        <v>53</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="J4" s="7" t="s">
-        <v>74</v>
+        <v>54</v>
       </c>
     </row>
     <row r="5" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>65</v>
+        <v>45</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="J5" s="7" t="s">
-        <v>76</v>
+        <v>56</v>
       </c>
     </row>
     <row r="6" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>65</v>
+        <v>45</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>77</v>
+        <v>57</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="J6" s="7" t="s">
-        <v>78</v>
+        <v>58</v>
       </c>
     </row>
     <row r="7" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>65</v>
+        <v>45</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>79</v>
+        <v>59</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="J7" s="7" t="s">
-        <v>80</v>
+        <v>60</v>
       </c>
     </row>
     <row r="8" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>65</v>
+        <v>45</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>81</v>
+        <v>61</v>
       </c>
       <c r="E8" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="G8" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="H8" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="I8" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="J8" s="7" t="s">
         <v>62</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="G8" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="H8" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="I8" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="J8" s="7" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="9" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>65</v>
+        <v>45</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="J9" s="7" t="s">
-        <v>84</v>
+        <v>64</v>
       </c>
     </row>
     <row r="10" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D10" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="B10" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>85</v>
-      </c>
       <c r="E10" s="3" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="J10" s="7" t="s">
-        <v>86</v>
+        <v>66</v>
       </c>
     </row>
     <row r="11" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>65</v>
+        <v>45</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="J11" s="7" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="G12" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="H12" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="I12" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="J12" s="7" t="s">
-        <v>92</v>
+        <v>68</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:J1"/>
-  <dataValidations count="5">
+  <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="G10:G11">
       <formula1>Listas!$C$2:$C$9</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="G12">
-      <formula1>Listas!$D$2:$D$21</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="G2">
       <formula1>Listas!$A$2:$A$3</formula1>
@@ -1749,766 +1579,766 @@
   <sheetData>
     <row r="1" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>93</v>
+        <v>69</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>94</v>
+        <v>70</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>95</v>
+        <v>71</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>96</v>
+        <v>72</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>56</v>
+        <v>36</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>57</v>
+        <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>97</v>
+        <v>73</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>91</v>
+        <v>74</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>27</v>
+        <v>75</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>98</v>
+        <v>76</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="I2" s="7" t="s">
-        <v>99</v>
+        <v>77</v>
       </c>
     </row>
     <row r="3" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>101</v>
+        <v>79</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>102</v>
+        <v>80</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>103</v>
+        <v>81</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>104</v>
+        <v>82</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="I3" s="7" t="s">
-        <v>105</v>
+        <v>83</v>
       </c>
     </row>
     <row r="4" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>106</v>
+        <v>84</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>91</v>
+        <v>74</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>27</v>
+        <v>75</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>98</v>
+        <v>76</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="I4" s="7" t="s">
-        <v>107</v>
+        <v>85</v>
       </c>
     </row>
     <row r="5" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>108</v>
+        <v>86</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>67</v>
+        <v>47</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>109</v>
+        <v>87</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>110</v>
+        <v>88</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>111</v>
+        <v>89</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="I5" s="7" t="s">
-        <v>112</v>
+        <v>90</v>
       </c>
     </row>
     <row r="6" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>113</v>
+        <v>91</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>91</v>
+        <v>74</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>39</v>
+        <v>92</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>114</v>
+        <v>93</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="I6" s="7" t="s">
-        <v>115</v>
+        <v>94</v>
       </c>
     </row>
     <row r="7" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>116</v>
+        <v>95</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>91</v>
+        <v>74</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>27</v>
+        <v>75</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>98</v>
+        <v>76</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="I7" s="7" t="s">
-        <v>117</v>
+        <v>96</v>
       </c>
     </row>
     <row r="8" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>118</v>
+        <v>97</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>91</v>
+        <v>74</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>35</v>
+        <v>98</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>119</v>
+        <v>99</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="I8" s="7" t="s">
-        <v>120</v>
+        <v>100</v>
       </c>
     </row>
     <row r="9" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>121</v>
+        <v>101</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>67</v>
+        <v>47</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>109</v>
+        <v>87</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>122</v>
+        <v>102</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>111</v>
+        <v>89</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="I9" s="7" t="s">
-        <v>123</v>
+        <v>103</v>
       </c>
     </row>
     <row r="10" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>124</v>
+        <v>104</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>91</v>
+        <v>74</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>35</v>
+        <v>98</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>119</v>
+        <v>99</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="I10" s="7" t="s">
-        <v>125</v>
+        <v>105</v>
       </c>
     </row>
     <row r="11" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>126</v>
+        <v>106</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>67</v>
+        <v>47</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>109</v>
+        <v>87</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>15</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>111</v>
+        <v>89</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="I11" s="7" t="s">
-        <v>127</v>
+        <v>107</v>
       </c>
     </row>
     <row r="12" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>128</v>
+        <v>108</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>91</v>
+        <v>74</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>35</v>
+        <v>98</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>119</v>
+        <v>99</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="I12" s="7" t="s">
-        <v>129</v>
+        <v>109</v>
       </c>
     </row>
     <row r="13" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>91</v>
+        <v>74</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>35</v>
+        <v>98</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>119</v>
+        <v>99</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="I13" s="7" t="s">
-        <v>131</v>
+        <v>111</v>
       </c>
     </row>
     <row r="14" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>132</v>
+        <v>112</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>91</v>
+        <v>74</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>35</v>
+        <v>98</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>119</v>
+        <v>99</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="I14" s="7" t="s">
-        <v>133</v>
+        <v>113</v>
       </c>
     </row>
     <row r="15" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>134</v>
+        <v>114</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>135</v>
+        <v>115</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>136</v>
+        <v>116</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>137</v>
+        <v>117</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>138</v>
+        <v>118</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="I15" s="7" t="s">
-        <v>139</v>
+        <v>119</v>
       </c>
     </row>
     <row r="16" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>91</v>
+        <v>74</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>35</v>
+        <v>98</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>119</v>
+        <v>99</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="I16" s="7" t="s">
-        <v>141</v>
+        <v>121</v>
       </c>
     </row>
     <row r="17" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>142</v>
+        <v>122</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>135</v>
+        <v>115</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>136</v>
+        <v>116</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>137</v>
+        <v>117</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>138</v>
+        <v>118</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="I17" s="7" t="s">
-        <v>143</v>
+        <v>123</v>
       </c>
     </row>
     <row r="18" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>144</v>
+        <v>124</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>91</v>
+        <v>74</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>35</v>
+        <v>98</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>119</v>
+        <v>99</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="I18" s="7" t="s">
-        <v>145</v>
+        <v>125</v>
       </c>
     </row>
     <row r="19" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>146</v>
+        <v>126</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>67</v>
+        <v>47</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>109</v>
+        <v>87</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>147</v>
+        <v>127</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>111</v>
+        <v>89</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="I19" s="7" t="s">
-        <v>148</v>
+        <v>128</v>
       </c>
     </row>
     <row r="20" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>149</v>
+        <v>129</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>91</v>
+        <v>74</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>31</v>
+        <v>130</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>150</v>
+        <v>131</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="I20" s="7" t="s">
-        <v>151</v>
+        <v>132</v>
       </c>
     </row>
     <row r="21" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>89</v>
+        <v>133</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>90</v>
+        <v>134</v>
       </c>
       <c r="C21" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="E21" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>153</v>
-      </c>
       <c r="F21" s="6" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="H21" s="6" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="I21" s="7" t="s">
-        <v>154</v>
+        <v>137</v>
       </c>
     </row>
     <row r="22" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>155</v>
+        <v>138</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>91</v>
+        <v>74</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>33</v>
+        <v>139</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>156</v>
+        <v>140</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="I22" s="7" t="s">
-        <v>157</v>
+        <v>141</v>
       </c>
     </row>
     <row r="23" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>158</v>
+        <v>142</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>91</v>
+        <v>74</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>33</v>
+        <v>139</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>156</v>
+        <v>140</v>
       </c>
       <c r="F23" s="6" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="G23" s="6" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="H23" s="6" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="I23" s="7" t="s">
-        <v>159</v>
+        <v>143</v>
       </c>
     </row>
     <row r="24" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>160</v>
+        <v>144</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>91</v>
+        <v>74</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>43</v>
+        <v>145</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>161</v>
+        <v>146</v>
       </c>
       <c r="F24" s="6" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="I24" s="7" t="s">
-        <v>162</v>
+        <v>147</v>
       </c>
     </row>
     <row r="25" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>163</v>
+        <v>148</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>91</v>
+        <v>74</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>35</v>
+        <v>98</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>119</v>
+        <v>99</v>
       </c>
       <c r="F25" s="6" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="G25" s="6" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="H25" s="6" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="I25" s="7" t="s">
-        <v>164</v>
+        <v>149</v>
       </c>
     </row>
     <row r="26" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>59</v>
+        <v>39</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>91</v>
+        <v>74</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>31</v>
+        <v>130</v>
       </c>
       <c r="E26" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="F26" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="G26" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="H26" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="I26" s="7" t="s">
         <v>150</v>
-      </c>
-      <c r="F26" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="G26" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="H26" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="I26" s="7" t="s">
-        <v>165</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:I1"/>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="F10:F26">
-      <formula1>Listas!$E$2:$E$3</formula1>
+      <formula1>Listas!$D$2:$D$3</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="F2:F26">
-      <formula1>Listas!$E$2:$E$3</formula1>
+      <formula1>Listas!$D$2:$D$3</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2535,34 +2365,34 @@
   <sheetData>
     <row r="1" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>166</v>
+        <v>151</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>167</v>
+        <v>152</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>168</v>
+        <v>153</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>169</v>
+        <v>154</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>170</v>
+        <v>155</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>95</v>
+        <v>71</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>56</v>
+        <v>36</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>57</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -2592,37 +2422,37 @@
   <sheetData>
     <row r="1" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>171</v>
+        <v>156</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>172</v>
+        <v>157</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>94</v>
+        <v>70</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>173</v>
+        <v>158</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>174</v>
+        <v>159</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>175</v>
+        <v>160</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>176</v>
+        <v>161</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="K1" s="5" t="s">
-        <v>177</v>
+        <v>162</v>
       </c>
     </row>
     <row r="2" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2630,34 +2460,34 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>97</v>
+        <v>73</v>
       </c>
       <c r="C2" s="3">
         <v>114</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>98</v>
+        <v>76</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>178</v>
+        <v>163</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>179</v>
+        <v>164</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="I2" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>181</v>
+        <v>166</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>182</v>
+        <v>167</v>
       </c>
     </row>
     <row r="3" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2665,34 +2495,34 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="C3" s="3">
         <v>126</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>104</v>
+        <v>82</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>183</v>
+        <v>168</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>184</v>
+        <v>169</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="I3" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>181</v>
+        <v>166</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>185</v>
+        <v>170</v>
       </c>
     </row>
     <row r="4" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2700,34 +2530,34 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>106</v>
+        <v>84</v>
       </c>
       <c r="C4" s="3">
         <v>52</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>98</v>
+        <v>76</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>178</v>
+        <v>163</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>179</v>
+        <v>164</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="I4" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>181</v>
+        <v>166</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>182</v>
+        <v>167</v>
       </c>
     </row>
     <row r="5" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2735,34 +2565,34 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>108</v>
+        <v>86</v>
       </c>
       <c r="C5" s="3">
         <v>72</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>111</v>
+        <v>89</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>186</v>
+        <v>171</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>187</v>
+        <v>172</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="I5" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>188</v>
+        <v>173</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>185</v>
+        <v>170</v>
       </c>
     </row>
     <row r="6" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2770,34 +2600,34 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>113</v>
+        <v>91</v>
       </c>
       <c r="C6" s="3">
         <v>452</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>114</v>
+        <v>93</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>178</v>
+        <v>163</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>179</v>
+        <v>164</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="I6" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>181</v>
+        <v>166</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>182</v>
+        <v>167</v>
       </c>
     </row>
     <row r="7" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2805,34 +2635,34 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>116</v>
+        <v>95</v>
       </c>
       <c r="C7" s="3">
         <v>178</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>98</v>
+        <v>76</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>178</v>
+        <v>163</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>179</v>
+        <v>164</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="I7" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>181</v>
+        <v>166</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>182</v>
+        <v>167</v>
       </c>
     </row>
     <row r="8" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2840,34 +2670,34 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>118</v>
+        <v>97</v>
       </c>
       <c r="C8" s="3">
         <v>82</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>119</v>
+        <v>99</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>178</v>
+        <v>163</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>179</v>
+        <v>164</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="I8" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>181</v>
+        <v>166</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>182</v>
+        <v>167</v>
       </c>
     </row>
     <row r="9" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2875,34 +2705,34 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>121</v>
+        <v>101</v>
       </c>
       <c r="C9" s="3">
         <v>180</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>111</v>
+        <v>89</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>186</v>
+        <v>171</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>187</v>
+        <v>172</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="I9" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>189</v>
+        <v>174</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>185</v>
+        <v>170</v>
       </c>
     </row>
     <row r="10" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2910,34 +2740,34 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>124</v>
+        <v>104</v>
       </c>
       <c r="C10" s="3">
         <v>44</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>119</v>
+        <v>99</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>178</v>
+        <v>163</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>179</v>
+        <v>164</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="I10" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>181</v>
+        <v>166</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>182</v>
+        <v>167</v>
       </c>
     </row>
     <row r="11" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2945,34 +2775,34 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>126</v>
+        <v>106</v>
       </c>
       <c r="C11" s="3">
         <v>4</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>111</v>
+        <v>89</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>186</v>
+        <v>171</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>187</v>
+        <v>172</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="I11" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>181</v>
+        <v>166</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>185</v>
+        <v>170</v>
       </c>
     </row>
     <row r="12" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2980,34 +2810,34 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>128</v>
+        <v>108</v>
       </c>
       <c r="C12" s="3">
         <v>18</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>119</v>
+        <v>99</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>178</v>
+        <v>163</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>179</v>
+        <v>164</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="I12" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>181</v>
+        <v>166</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>182</v>
+        <v>167</v>
       </c>
     </row>
     <row r="13" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3015,34 +2845,34 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>66</v>
+        <v>46</v>
       </c>
       <c r="C13" s="3">
         <v>4</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>190</v>
+        <v>175</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>186</v>
+        <v>171</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>187</v>
+        <v>172</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>191</v>
+        <v>176</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>185</v>
+        <v>170</v>
       </c>
     </row>
     <row r="14" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3050,34 +2880,34 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="C14" s="3">
         <v>2</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>119</v>
+        <v>99</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>178</v>
+        <v>163</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>179</v>
+        <v>164</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>181</v>
+        <v>166</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>182</v>
+        <v>167</v>
       </c>
     </row>
     <row r="15" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3085,34 +2915,34 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="C15" s="3">
         <v>40</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>192</v>
+        <v>177</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>193</v>
+        <v>178</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>194</v>
+        <v>179</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>191</v>
+        <v>176</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>185</v>
+        <v>170</v>
       </c>
     </row>
     <row r="16" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3120,34 +2950,34 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>132</v>
+        <v>112</v>
       </c>
       <c r="C16" s="3">
         <v>70</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>119</v>
+        <v>99</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>178</v>
+        <v>163</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>179</v>
+        <v>164</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="I16" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>181</v>
+        <v>166</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>182</v>
+        <v>167</v>
       </c>
     </row>
     <row r="17" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3155,34 +2985,34 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>134</v>
+        <v>114</v>
       </c>
       <c r="C17" s="3">
         <v>14</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>138</v>
+        <v>118</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>195</v>
+        <v>180</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>196</v>
+        <v>181</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="I17" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>197</v>
+        <v>182</v>
       </c>
       <c r="K17" s="3" t="s">
-        <v>185</v>
+        <v>170</v>
       </c>
     </row>
     <row r="18" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3190,34 +3020,34 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="C18" s="3">
         <v>2</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>119</v>
+        <v>99</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>178</v>
+        <v>163</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>179</v>
+        <v>164</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="I18" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>181</v>
+        <v>166</v>
       </c>
       <c r="K18" s="3" t="s">
-        <v>182</v>
+        <v>167</v>
       </c>
     </row>
     <row r="19" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3225,34 +3055,34 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>142</v>
+        <v>122</v>
       </c>
       <c r="C19" s="3">
         <v>14</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>138</v>
+        <v>118</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>195</v>
+        <v>180</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>196</v>
+        <v>181</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="I19" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>197</v>
+        <v>182</v>
       </c>
       <c r="K19" s="3" t="s">
-        <v>185</v>
+        <v>170</v>
       </c>
     </row>
     <row r="20" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3260,34 +3090,34 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>144</v>
+        <v>124</v>
       </c>
       <c r="C20" s="3">
         <v>86</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>119</v>
+        <v>99</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>178</v>
+        <v>163</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>179</v>
+        <v>164</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="I20" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>181</v>
+        <v>166</v>
       </c>
       <c r="K20" s="3" t="s">
-        <v>182</v>
+        <v>167</v>
       </c>
     </row>
     <row r="21" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3295,34 +3125,34 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>146</v>
+        <v>126</v>
       </c>
       <c r="C21" s="3">
         <v>80</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>111</v>
+        <v>89</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>186</v>
+        <v>171</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>187</v>
+        <v>172</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="I21" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>198</v>
+        <v>183</v>
       </c>
       <c r="K21" s="3" t="s">
-        <v>185</v>
+        <v>170</v>
       </c>
     </row>
     <row r="22" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3330,34 +3160,34 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>149</v>
+        <v>129</v>
       </c>
       <c r="C22" s="3">
         <v>252</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>150</v>
+        <v>131</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>178</v>
+        <v>163</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>179</v>
+        <v>164</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="I22" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>181</v>
+        <v>166</v>
       </c>
       <c r="K22" s="3" t="s">
-        <v>182</v>
+        <v>167</v>
       </c>
     </row>
     <row r="23" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3365,34 +3195,34 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>89</v>
+        <v>133</v>
       </c>
       <c r="C23" s="3">
         <v>2</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>153</v>
+        <v>136</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>199</v>
+        <v>184</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>200</v>
+        <v>185</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>201</v>
+        <v>13</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>197</v>
+        <v>182</v>
       </c>
       <c r="K23" s="3" t="s">
-        <v>185</v>
+        <v>170</v>
       </c>
     </row>
     <row r="24" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3400,34 +3230,34 @@
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>155</v>
+        <v>138</v>
       </c>
       <c r="C24" s="3">
         <v>142</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>156</v>
+        <v>140</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>178</v>
+        <v>163</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>179</v>
+        <v>164</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="I24" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>181</v>
+        <v>166</v>
       </c>
       <c r="K24" s="3" t="s">
-        <v>182</v>
+        <v>167</v>
       </c>
     </row>
     <row r="25" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3435,34 +3265,34 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>202</v>
+        <v>186</v>
       </c>
       <c r="C25" s="3">
         <v>110</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>203</v>
+        <v>187</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>204</v>
+        <v>188</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>205</v>
+        <v>189</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="I25" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="K25" s="3" t="s">
-        <v>185</v>
+        <v>170</v>
       </c>
     </row>
     <row r="26" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3470,34 +3300,34 @@
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>158</v>
+        <v>142</v>
       </c>
       <c r="C26" s="3">
         <v>176</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>156</v>
+        <v>140</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>178</v>
+        <v>163</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>179</v>
+        <v>164</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="I26" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>181</v>
+        <v>166</v>
       </c>
       <c r="K26" s="3" t="s">
-        <v>182</v>
+        <v>167</v>
       </c>
     </row>
     <row r="27" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3505,34 +3335,34 @@
         <v>26</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>160</v>
+        <v>144</v>
       </c>
       <c r="C27" s="3">
         <v>120</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>161</v>
+        <v>146</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>178</v>
+        <v>163</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>179</v>
+        <v>164</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="I27" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>181</v>
+        <v>166</v>
       </c>
       <c r="K27" s="3" t="s">
-        <v>182</v>
+        <v>167</v>
       </c>
     </row>
     <row r="28" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3540,34 +3370,34 @@
         <v>27</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>163</v>
+        <v>148</v>
       </c>
       <c r="C28" s="3">
         <v>468</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>119</v>
+        <v>99</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>178</v>
+        <v>163</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>179</v>
+        <v>164</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="I28" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>181</v>
+        <v>166</v>
       </c>
       <c r="K28" s="3" t="s">
-        <v>182</v>
+        <v>167</v>
       </c>
     </row>
     <row r="29" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3575,34 +3405,34 @@
         <v>28</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>59</v>
+        <v>39</v>
       </c>
       <c r="C29" s="3">
         <v>189</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>150</v>
+        <v>131</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>178</v>
+        <v>163</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>179</v>
+        <v>164</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>206</v>
+        <v>190</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>181</v>
+        <v>166</v>
       </c>
       <c r="K29" s="3" t="s">
-        <v>182</v>
+        <v>167</v>
       </c>
     </row>
   </sheetData>

--- a/docs/dominio-metrico/migracion/cuestionarios/el-conde-de-sex.xlsx
+++ b/docs/dominio-metrico/migracion/cuestionarios/el-conde-de-sex.xlsx
@@ -141,7 +141,7 @@
     <t>Romance · Octosílabo</t>
   </si>
   <si>
-    <t>Tiene 189 versos, y un romance octosílabo no puede tener un número impar: en algún punto falta o sobra un verso. Hay que localizarlo y decir si se trata de una laguna, en cuyo caso renumeraré la obra a partir de ahí, o de un error en el rango, en cuyo caso hace falta el rango correcto. Las preguntas que dependen de cómo se reparta en estrofas te las haré cuando esto esté claro.</t>
+    <t>Tiene 189 versos, y un romance octosílabo no puede tener un número impar: en algún punto falta o sobra un verso. Hay que localizarlo y decir si se trata de una laguna, en cuyo caso renumeraré la obra a partir de ahí, o de un error en el rango, en cuyo caso hace falta el rango correcto.</t>
   </si>
   <si>
     <t/>

--- a/docs/dominio-metrico/migracion/cuestionarios/el-conde-de-sex.xlsx
+++ b/docs/dominio-metrico/migracion/cuestionarios/el-conde-de-sex.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="648" uniqueCount="191">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="578" uniqueCount="178">
   <si>
     <t>Migración métrica · El conde de Sex</t>
   </si>
@@ -27,7 +27,7 @@
     <t>El Excel tiene cinco pestañas. En tres de ellas hay que escribir —Responder, Confirmar y Desviaciones— y las otras dos son de consulta: Secuencias, con todo lo que tiene anotado tu obra, e Instrucciones, donde estás ahora. Solo hace falta escribir en las columnas de fondo amarillo, que son «Respuesta», «Excepciones / detalle» y «Comentario». El resto de columnas las genera el programa y las necesita tal cual para poder leer las respuestas, así que conviene no tocarlas.</t>
   </si>
   <si>
-    <t>En Responder están las preguntas que no he podido contestar con lo que ya tenías anotado. Cada fila corresponde a un pasaje y a una pregunta. Cuando la celda tiene desplegable, basta con elegir; cuando no, la columna «Cómo contestar» explica el formato. Las preguntas que se refieren a cada estrofa aparecen de dos maneras: si son pocas estrofas, hay una fila por estrofa; si son muchas, hay una sola fila cuya respuesta vale para todas, y las estrofas que se aparten de ella se anotan en «Excepciones / detalle» indicando los versos y la respuesta, por ejemplo «191–194: Cruzada · abab; 203–206: Cruzada · abab».</t>
+    <t>En Responder están las preguntas que no he podido contestar con lo que ya tenías anotado. Cada fila corresponde a un pasaje y a una pregunta, también cuando la pregunta es de cada estrofa: se contesta una vez y la respuesta vale para todas, y las estrofas que se aparten se anotan en «Excepciones / detalle» como «versos: esquema», por ejemplo «191-194: abab; 203-206: abab». Cuando la celda tiene desplegable, basta con elegir; cuando no, la columna «Cómo contestar» explica el formato.</t>
   </si>
   <si>
     <t>Las filas marcadas como Decidir señalan pasajes cuyo número de versos no encaja con la forma que tienen asignada. En ellas hay que elegir en el desplegable qué ocurre y explicarlo al lado. Si se trata de una laguna que no se contó, indica en qué verso está y cuántos versos faltan, porque los añadiré a la numeración y todo lo que viene después se desplazará. Si lo que falla es el rango, escribe el rango correcto.</t>
@@ -54,7 +54,7 @@
     <t>Esquema de rima: una letra por verso, en mayúscula si el verso es de arte mayor y un guion si queda suelto. Por ejemplo, «aBab-B».</t>
   </si>
   <si>
-    <t>Excepciones: los versos de la estrofa y la respuesta que le corresponde, separando cada estrofa con punto y coma. Por ejemplo, «191–194: Cruzada · abab; 203–206: Cruzada · abab».</t>
+    <t>Excepciones: los versos de la estrofa y su esquema, separados por dos puntos, y cada estrofa de la siguiente con punto y coma. Por ejemplo, «191-194: abab; 203-206: abab». El esquema se escribe como arriba: una letra por verso, en mayúscula si el verso es de arte mayor.</t>
   </si>
   <si>
     <t>lista</t>
@@ -177,52 +177,13 @@
     <t>Quintilla · Octosílaba consonante</t>
   </si>
   <si>
-    <t>Esquema de rima · estrofa 1 (vv. 1329–1333)</t>
-  </si>
-  <si>
-    <t>U|0cbaa6dc-b3e1-4f2b-bba6-1317c0a9c141|a43860ff-566c-4a0b-b210-4572b8d7b066|1329</t>
-  </si>
-  <si>
-    <t>Esquema de rima · estrofa 2 (vv. 1334–1338)</t>
-  </si>
-  <si>
-    <t>U|0cbaa6dc-b3e1-4f2b-bba6-1317c0a9c141|a43860ff-566c-4a0b-b210-4572b8d7b066|1334</t>
-  </si>
-  <si>
-    <t>Esquema de rima · estrofa 3 (vv. 1339–1343)</t>
-  </si>
-  <si>
-    <t>U|0cbaa6dc-b3e1-4f2b-bba6-1317c0a9c141|a43860ff-566c-4a0b-b210-4572b8d7b066|1339</t>
-  </si>
-  <si>
-    <t>Esquema de rima · estrofa 4 (vv. 1344–1348)</t>
-  </si>
-  <si>
-    <t>U|0cbaa6dc-b3e1-4f2b-bba6-1317c0a9c141|a43860ff-566c-4a0b-b210-4572b8d7b066|1344</t>
-  </si>
-  <si>
-    <t>Esquema de rima · estrofa 5 (vv. 1349–1353)</t>
-  </si>
-  <si>
-    <t>U|0cbaa6dc-b3e1-4f2b-bba6-1317c0a9c141|a43860ff-566c-4a0b-b210-4572b8d7b066|1349</t>
-  </si>
-  <si>
-    <t>Esquema de rima · estrofa 6 (vv. 1354–1358)</t>
-  </si>
-  <si>
-    <t>U|0cbaa6dc-b3e1-4f2b-bba6-1317c0a9c141|a43860ff-566c-4a0b-b210-4572b8d7b066|1354</t>
-  </si>
-  <si>
-    <t>Esquema de rima · estrofa 7 (vv. 1359–1363)</t>
-  </si>
-  <si>
-    <t>U|0cbaa6dc-b3e1-4f2b-bba6-1317c0a9c141|a43860ff-566c-4a0b-b210-4572b8d7b066|1359</t>
-  </si>
-  <si>
-    <t>Esquema de rima · estrofa 8 (vv. 1364–1368)</t>
-  </si>
-  <si>
-    <t>U|0cbaa6dc-b3e1-4f2b-bba6-1317c0a9c141|a43860ff-566c-4a0b-b210-4572b8d7b066|1364</t>
+    <t>Esquema de rima · 8 estrofas</t>
+  </si>
+  <si>
+    <t>Elige en el desplegable. La respuesta vale para todas las estrofas; las que sean distintas, en «Excepciones», como «191-194: abab»</t>
+  </si>
+  <si>
+    <t>R|0cbaa6dc-b3e1-4f2b-bba6-1317c0a9c141|a43860ff-566c-4a0b-b210-4572b8d7b066</t>
   </si>
   <si>
     <t>Pregunta</t>
@@ -1174,7 +1135,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:J4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="2" width="11" customWidth="1"/>
@@ -1301,7 +1262,7 @@
         <v>42</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="G4" s="6" t="s">
         <v>42</v>
@@ -1313,246 +1274,19 @@
         <v>42</v>
       </c>
       <c r="J4" s="7" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="D5" s="3" t="s">
         <v>55</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="G5" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="H5" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="I5" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="J5" s="7" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="G6" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="H6" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="I6" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="J6" s="7" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="G7" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="H7" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="I7" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="J7" s="7" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="G8" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="H8" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="I8" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="J8" s="7" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="G9" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="H9" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="I9" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="J9" s="7" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="G10" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="H10" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="I10" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="J10" s="7" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="G11" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="H11" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="I11" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="J11" s="7" t="s">
-        <v>68</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:J1"/>
-  <dataValidations count="4">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="G10:G11">
-      <formula1>Listas!$C$2:$C$9</formula1>
-    </dataValidation>
+  <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="G2">
       <formula1>Listas!$A$2:$A$3</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="G3">
       <formula1>Listas!$B$2:$B$3</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="G4:G11">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="G4">
       <formula1>Listas!$C$2:$C$9</formula1>
     </dataValidation>
   </dataValidations>
@@ -1585,19 +1319,19 @@
         <v>30</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>69</v>
+        <v>56</v>
       </c>
       <c r="D1" s="5" t="s">
         <v>34</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>71</v>
+        <v>58</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>72</v>
+        <v>59</v>
       </c>
       <c r="H1" s="5" t="s">
         <v>36</v>
@@ -1608,19 +1342,19 @@
     </row>
     <row r="2" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>73</v>
+        <v>60</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>40</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>74</v>
+        <v>61</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>76</v>
+        <v>63</v>
       </c>
       <c r="F2" s="6" t="s">
         <v>42</v>
@@ -1632,24 +1366,24 @@
         <v>42</v>
       </c>
       <c r="I2" s="7" t="s">
-        <v>77</v>
+        <v>64</v>
       </c>
     </row>
     <row r="3" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>78</v>
+        <v>65</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>80</v>
+        <v>67</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>81</v>
+        <v>68</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>82</v>
+        <v>69</v>
       </c>
       <c r="F3" s="6" t="s">
         <v>42</v>
@@ -1661,24 +1395,24 @@
         <v>42</v>
       </c>
       <c r="I3" s="7" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
     </row>
     <row r="4" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>84</v>
+        <v>71</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>40</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>74</v>
+        <v>61</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>76</v>
+        <v>63</v>
       </c>
       <c r="F4" s="6" t="s">
         <v>42</v>
@@ -1690,24 +1424,24 @@
         <v>42</v>
       </c>
       <c r="I4" s="7" t="s">
-        <v>85</v>
+        <v>72</v>
       </c>
     </row>
     <row r="5" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>86</v>
+        <v>73</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>47</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>87</v>
+        <v>74</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>89</v>
+        <v>76</v>
       </c>
       <c r="F5" s="6" t="s">
         <v>42</v>
@@ -1719,24 +1453,24 @@
         <v>42</v>
       </c>
       <c r="I5" s="7" t="s">
-        <v>90</v>
+        <v>77</v>
       </c>
     </row>
     <row r="6" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>40</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>74</v>
+        <v>61</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="F6" s="6" t="s">
         <v>42</v>
@@ -1748,24 +1482,24 @@
         <v>42</v>
       </c>
       <c r="I6" s="7" t="s">
-        <v>94</v>
+        <v>81</v>
       </c>
     </row>
     <row r="7" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>40</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>74</v>
+        <v>61</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>76</v>
+        <v>63</v>
       </c>
       <c r="F7" s="6" t="s">
         <v>42</v>
@@ -1777,24 +1511,24 @@
         <v>42</v>
       </c>
       <c r="I7" s="7" t="s">
-        <v>96</v>
+        <v>83</v>
       </c>
     </row>
     <row r="8" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>40</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>74</v>
+        <v>61</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>98</v>
+        <v>85</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="F8" s="6" t="s">
         <v>42</v>
@@ -1806,24 +1540,24 @@
         <v>42</v>
       </c>
       <c r="I8" s="7" t="s">
-        <v>100</v>
+        <v>87</v>
       </c>
     </row>
     <row r="9" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>101</v>
+        <v>88</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>47</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>87</v>
+        <v>74</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>102</v>
+        <v>89</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>89</v>
+        <v>76</v>
       </c>
       <c r="F9" s="6" t="s">
         <v>42</v>
@@ -1835,24 +1569,24 @@
         <v>42</v>
       </c>
       <c r="I9" s="7" t="s">
-        <v>103</v>
+        <v>90</v>
       </c>
     </row>
     <row r="10" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>40</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>74</v>
+        <v>61</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>98</v>
+        <v>85</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="F10" s="6" t="s">
         <v>42</v>
@@ -1864,24 +1598,24 @@
         <v>42</v>
       </c>
       <c r="I10" s="7" t="s">
-        <v>105</v>
+        <v>92</v>
       </c>
     </row>
     <row r="11" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>106</v>
+        <v>93</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>47</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>87</v>
+        <v>74</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>15</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>89</v>
+        <v>76</v>
       </c>
       <c r="F11" s="6" t="s">
         <v>42</v>
@@ -1893,24 +1627,24 @@
         <v>42</v>
       </c>
       <c r="I11" s="7" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
     </row>
     <row r="12" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>40</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>74</v>
+        <v>61</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>98</v>
+        <v>85</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="F12" s="6" t="s">
         <v>42</v>
@@ -1922,53 +1656,53 @@
         <v>42</v>
       </c>
       <c r="I12" s="7" t="s">
-        <v>109</v>
+        <v>96</v>
       </c>
     </row>
     <row r="13" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>110</v>
+        <v>97</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>40</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>74</v>
+        <v>61</v>
       </c>
       <c r="D13" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="F13" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="G13" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="H13" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="I13" s="7" t="s">
         <v>98</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="F13" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="G13" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="H13" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="I13" s="7" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="14" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>112</v>
+        <v>99</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>40</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>74</v>
+        <v>61</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>98</v>
+        <v>85</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="F14" s="6" t="s">
         <v>42</v>
@@ -1980,24 +1714,24 @@
         <v>42</v>
       </c>
       <c r="I14" s="7" t="s">
-        <v>113</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>114</v>
+        <v>101</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>115</v>
+        <v>102</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>116</v>
+        <v>103</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>117</v>
+        <v>104</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>118</v>
+        <v>105</v>
       </c>
       <c r="F15" s="6" t="s">
         <v>42</v>
@@ -2009,24 +1743,24 @@
         <v>42</v>
       </c>
       <c r="I15" s="7" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
     </row>
     <row r="16" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>120</v>
+        <v>107</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>40</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>74</v>
+        <v>61</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>98</v>
+        <v>85</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>42</v>
@@ -2038,24 +1772,24 @@
         <v>42</v>
       </c>
       <c r="I16" s="7" t="s">
-        <v>121</v>
+        <v>108</v>
       </c>
     </row>
     <row r="17" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>122</v>
+        <v>109</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>115</v>
+        <v>102</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>116</v>
+        <v>103</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>117</v>
+        <v>104</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>118</v>
+        <v>105</v>
       </c>
       <c r="F17" s="6" t="s">
         <v>42</v>
@@ -2067,24 +1801,24 @@
         <v>42</v>
       </c>
       <c r="I17" s="7" t="s">
-        <v>123</v>
+        <v>110</v>
       </c>
     </row>
     <row r="18" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>124</v>
+        <v>111</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>40</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>74</v>
+        <v>61</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>98</v>
+        <v>85</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>42</v>
@@ -2096,24 +1830,24 @@
         <v>42</v>
       </c>
       <c r="I18" s="7" t="s">
-        <v>125</v>
+        <v>112</v>
       </c>
     </row>
     <row r="19" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>126</v>
+        <v>113</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>47</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>87</v>
+        <v>74</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>127</v>
+        <v>114</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>89</v>
+        <v>76</v>
       </c>
       <c r="F19" s="6" t="s">
         <v>42</v>
@@ -2125,24 +1859,24 @@
         <v>42</v>
       </c>
       <c r="I19" s="7" t="s">
-        <v>128</v>
+        <v>115</v>
       </c>
     </row>
     <row r="20" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>129</v>
+        <v>116</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>40</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>74</v>
+        <v>61</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>130</v>
+        <v>117</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>131</v>
+        <v>118</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>42</v>
@@ -2154,24 +1888,24 @@
         <v>42</v>
       </c>
       <c r="I20" s="7" t="s">
-        <v>132</v>
+        <v>119</v>
       </c>
     </row>
     <row r="21" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>133</v>
+        <v>120</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>134</v>
+        <v>121</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>116</v>
+        <v>103</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>135</v>
+        <v>122</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>136</v>
+        <v>123</v>
       </c>
       <c r="F21" s="6" t="s">
         <v>42</v>
@@ -2183,24 +1917,24 @@
         <v>42</v>
       </c>
       <c r="I21" s="7" t="s">
-        <v>137</v>
+        <v>124</v>
       </c>
     </row>
     <row r="22" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>138</v>
+        <v>125</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>40</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>74</v>
+        <v>61</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>139</v>
+        <v>126</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>140</v>
+        <v>127</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>42</v>
@@ -2212,24 +1946,24 @@
         <v>42</v>
       </c>
       <c r="I22" s="7" t="s">
-        <v>141</v>
+        <v>128</v>
       </c>
     </row>
     <row r="23" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>142</v>
+        <v>129</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>40</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>74</v>
+        <v>61</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>139</v>
+        <v>126</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>140</v>
+        <v>127</v>
       </c>
       <c r="F23" s="6" t="s">
         <v>42</v>
@@ -2241,24 +1975,24 @@
         <v>42</v>
       </c>
       <c r="I23" s="7" t="s">
-        <v>143</v>
+        <v>130</v>
       </c>
     </row>
     <row r="24" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>144</v>
+        <v>131</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>40</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>74</v>
+        <v>61</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>145</v>
+        <v>132</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>146</v>
+        <v>133</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>42</v>
@@ -2270,24 +2004,24 @@
         <v>42</v>
       </c>
       <c r="I24" s="7" t="s">
-        <v>147</v>
+        <v>134</v>
       </c>
     </row>
     <row r="25" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>148</v>
+        <v>135</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>40</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>74</v>
+        <v>61</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>98</v>
+        <v>85</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="F25" s="6" t="s">
         <v>42</v>
@@ -2299,7 +2033,7 @@
         <v>42</v>
       </c>
       <c r="I25" s="7" t="s">
-        <v>149</v>
+        <v>136</v>
       </c>
     </row>
     <row r="26" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2310,13 +2044,13 @@
         <v>40</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>74</v>
+        <v>61</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>130</v>
+        <v>117</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>131</v>
+        <v>118</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>42</v>
@@ -2328,7 +2062,7 @@
         <v>42</v>
       </c>
       <c r="I26" s="7" t="s">
-        <v>150</v>
+        <v>137</v>
       </c>
     </row>
   </sheetData>
@@ -2371,22 +2105,22 @@
         <v>29</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>151</v>
+        <v>138</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>152</v>
+        <v>139</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>153</v>
+        <v>140</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>154</v>
+        <v>141</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>155</v>
+        <v>142</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>71</v>
+        <v>58</v>
       </c>
       <c r="I1" s="5" t="s">
         <v>36</v>
@@ -2422,37 +2156,37 @@
   <sheetData>
     <row r="1" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>156</v>
+        <v>143</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>29</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>157</v>
+        <v>144</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="E1" s="5" t="s">
         <v>30</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>158</v>
+        <v>145</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>160</v>
+        <v>147</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>161</v>
+        <v>148</v>
       </c>
       <c r="J1" s="5" t="s">
         <v>32</v>
       </c>
       <c r="K1" s="5" t="s">
-        <v>162</v>
+        <v>149</v>
       </c>
     </row>
     <row r="2" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2460,34 +2194,34 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>73</v>
+        <v>60</v>
       </c>
       <c r="C2" s="3">
         <v>114</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>76</v>
+        <v>63</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>163</v>
+        <v>150</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>164</v>
+        <v>151</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="I2" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>166</v>
+        <v>153</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>167</v>
+        <v>154</v>
       </c>
     </row>
     <row r="3" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2495,34 +2229,34 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>78</v>
+        <v>65</v>
       </c>
       <c r="C3" s="3">
         <v>126</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>82</v>
+        <v>69</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>168</v>
+        <v>155</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>169</v>
+        <v>156</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="I3" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>166</v>
+        <v>153</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>170</v>
+        <v>157</v>
       </c>
     </row>
     <row r="4" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2530,34 +2264,34 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>84</v>
+        <v>71</v>
       </c>
       <c r="C4" s="3">
         <v>52</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>76</v>
+        <v>63</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>163</v>
+        <v>150</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>164</v>
+        <v>151</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="I4" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>166</v>
+        <v>153</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>167</v>
+        <v>154</v>
       </c>
     </row>
     <row r="5" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2565,34 +2299,34 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>86</v>
+        <v>73</v>
       </c>
       <c r="C5" s="3">
         <v>72</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>89</v>
+        <v>76</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>171</v>
+        <v>158</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>172</v>
+        <v>159</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="I5" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>173</v>
+        <v>160</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>170</v>
+        <v>157</v>
       </c>
     </row>
     <row r="6" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2600,34 +2334,34 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="C6" s="3">
         <v>452</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>163</v>
+        <v>150</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>164</v>
+        <v>151</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="I6" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>166</v>
+        <v>153</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>167</v>
+        <v>154</v>
       </c>
     </row>
     <row r="7" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2635,34 +2369,34 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="C7" s="3">
         <v>178</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>76</v>
+        <v>63</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>163</v>
+        <v>150</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>164</v>
+        <v>151</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="I7" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>166</v>
+        <v>153</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>167</v>
+        <v>154</v>
       </c>
     </row>
     <row r="8" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2670,34 +2404,34 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="C8" s="3">
         <v>82</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>163</v>
+        <v>150</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>164</v>
+        <v>151</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="I8" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>166</v>
+        <v>153</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>167</v>
+        <v>154</v>
       </c>
     </row>
     <row r="9" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2705,34 +2439,34 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>101</v>
+        <v>88</v>
       </c>
       <c r="C9" s="3">
         <v>180</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>89</v>
+        <v>76</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>171</v>
+        <v>158</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>172</v>
+        <v>159</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="I9" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>174</v>
+        <v>161</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>170</v>
+        <v>157</v>
       </c>
     </row>
     <row r="10" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2740,34 +2474,34 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="C10" s="3">
         <v>44</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>163</v>
+        <v>150</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>164</v>
+        <v>151</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="I10" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>166</v>
+        <v>153</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>167</v>
+        <v>154</v>
       </c>
     </row>
     <row r="11" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2775,34 +2509,34 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>106</v>
+        <v>93</v>
       </c>
       <c r="C11" s="3">
         <v>4</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>89</v>
+        <v>76</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>171</v>
+        <v>158</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>172</v>
+        <v>159</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="I11" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>166</v>
+        <v>153</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>170</v>
+        <v>157</v>
       </c>
     </row>
     <row r="12" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2810,34 +2544,34 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="C12" s="3">
         <v>18</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>163</v>
+        <v>150</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>164</v>
+        <v>151</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="I12" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>166</v>
+        <v>153</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>167</v>
+        <v>154</v>
       </c>
     </row>
     <row r="13" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2851,28 +2585,28 @@
         <v>4</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>175</v>
+        <v>162</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>171</v>
+        <v>158</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>172</v>
+        <v>159</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>176</v>
+        <v>163</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>170</v>
+        <v>157</v>
       </c>
     </row>
     <row r="14" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2880,34 +2614,34 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>110</v>
+        <v>97</v>
       </c>
       <c r="C14" s="3">
         <v>2</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>163</v>
+        <v>150</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>164</v>
+        <v>151</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>166</v>
+        <v>153</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>167</v>
+        <v>154</v>
       </c>
     </row>
     <row r="15" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2921,28 +2655,28 @@
         <v>40</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>177</v>
+        <v>164</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>178</v>
+        <v>165</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>179</v>
+        <v>166</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>176</v>
+        <v>163</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>170</v>
+        <v>157</v>
       </c>
     </row>
     <row r="16" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2950,34 +2684,34 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>112</v>
+        <v>99</v>
       </c>
       <c r="C16" s="3">
         <v>70</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>163</v>
+        <v>150</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>164</v>
+        <v>151</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="I16" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>166</v>
+        <v>153</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>167</v>
+        <v>154</v>
       </c>
     </row>
     <row r="17" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2985,34 +2719,34 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>114</v>
+        <v>101</v>
       </c>
       <c r="C17" s="3">
         <v>14</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>118</v>
+        <v>105</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>180</v>
+        <v>167</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>181</v>
+        <v>168</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="I17" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>182</v>
+        <v>169</v>
       </c>
       <c r="K17" s="3" t="s">
-        <v>170</v>
+        <v>157</v>
       </c>
     </row>
     <row r="18" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3020,34 +2754,34 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>120</v>
+        <v>107</v>
       </c>
       <c r="C18" s="3">
         <v>2</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>163</v>
+        <v>150</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>164</v>
+        <v>151</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="I18" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>166</v>
+        <v>153</v>
       </c>
       <c r="K18" s="3" t="s">
-        <v>167</v>
+        <v>154</v>
       </c>
     </row>
     <row r="19" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3055,34 +2789,34 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>122</v>
+        <v>109</v>
       </c>
       <c r="C19" s="3">
         <v>14</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>118</v>
+        <v>105</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>180</v>
+        <v>167</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>181</v>
+        <v>168</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="I19" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>182</v>
+        <v>169</v>
       </c>
       <c r="K19" s="3" t="s">
-        <v>170</v>
+        <v>157</v>
       </c>
     </row>
     <row r="20" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3090,34 +2824,34 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>124</v>
+        <v>111</v>
       </c>
       <c r="C20" s="3">
         <v>86</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>163</v>
+        <v>150</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>164</v>
+        <v>151</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="I20" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>166</v>
+        <v>153</v>
       </c>
       <c r="K20" s="3" t="s">
-        <v>167</v>
+        <v>154</v>
       </c>
     </row>
     <row r="21" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3125,34 +2859,34 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>126</v>
+        <v>113</v>
       </c>
       <c r="C21" s="3">
         <v>80</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>89</v>
+        <v>76</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>171</v>
+        <v>158</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>172</v>
+        <v>159</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="I21" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>183</v>
+        <v>170</v>
       </c>
       <c r="K21" s="3" t="s">
-        <v>170</v>
+        <v>157</v>
       </c>
     </row>
     <row r="22" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3160,34 +2894,34 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>129</v>
+        <v>116</v>
       </c>
       <c r="C22" s="3">
         <v>252</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>131</v>
+        <v>118</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>163</v>
+        <v>150</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>164</v>
+        <v>151</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="I22" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>166</v>
+        <v>153</v>
       </c>
       <c r="K22" s="3" t="s">
-        <v>167</v>
+        <v>154</v>
       </c>
     </row>
     <row r="23" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3195,34 +2929,34 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>133</v>
+        <v>120</v>
       </c>
       <c r="C23" s="3">
         <v>2</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>136</v>
+        <v>123</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>184</v>
+        <v>171</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>185</v>
+        <v>172</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="I23" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>182</v>
+        <v>169</v>
       </c>
       <c r="K23" s="3" t="s">
-        <v>170</v>
+        <v>157</v>
       </c>
     </row>
     <row r="24" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3230,34 +2964,34 @@
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>138</v>
+        <v>125</v>
       </c>
       <c r="C24" s="3">
         <v>142</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>140</v>
+        <v>127</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>163</v>
+        <v>150</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>164</v>
+        <v>151</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="I24" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>166</v>
+        <v>153</v>
       </c>
       <c r="K24" s="3" t="s">
-        <v>167</v>
+        <v>154</v>
       </c>
     </row>
     <row r="25" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3265,34 +2999,34 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>186</v>
+        <v>173</v>
       </c>
       <c r="C25" s="3">
         <v>110</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>187</v>
+        <v>174</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>188</v>
+        <v>175</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>189</v>
+        <v>176</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="I25" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="K25" s="3" t="s">
-        <v>170</v>
+        <v>157</v>
       </c>
     </row>
     <row r="26" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3300,34 +3034,34 @@
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>142</v>
+        <v>129</v>
       </c>
       <c r="C26" s="3">
         <v>176</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>140</v>
+        <v>127</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>163</v>
+        <v>150</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>164</v>
+        <v>151</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="I26" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>166</v>
+        <v>153</v>
       </c>
       <c r="K26" s="3" t="s">
-        <v>167</v>
+        <v>154</v>
       </c>
     </row>
     <row r="27" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3335,34 +3069,34 @@
         <v>26</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>144</v>
+        <v>131</v>
       </c>
       <c r="C27" s="3">
         <v>120</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>146</v>
+        <v>133</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>163</v>
+        <v>150</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>164</v>
+        <v>151</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="I27" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>166</v>
+        <v>153</v>
       </c>
       <c r="K27" s="3" t="s">
-        <v>167</v>
+        <v>154</v>
       </c>
     </row>
     <row r="28" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3370,34 +3104,34 @@
         <v>27</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>148</v>
+        <v>135</v>
       </c>
       <c r="C28" s="3">
         <v>468</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>163</v>
+        <v>150</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>164</v>
+        <v>151</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="I28" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>166</v>
+        <v>153</v>
       </c>
       <c r="K28" s="3" t="s">
-        <v>167</v>
+        <v>154</v>
       </c>
     </row>
     <row r="29" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3411,28 +3145,28 @@
         <v>189</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>131</v>
+        <v>118</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>163</v>
+        <v>150</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>164</v>
+        <v>151</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>190</v>
+        <v>177</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>166</v>
+        <v>153</v>
       </c>
       <c r="K29" s="3" t="s">
-        <v>167</v>
+        <v>154</v>
       </c>
     </row>
   </sheetData>

--- a/docs/dominio-metrico/migracion/cuestionarios/el-conde-de-sex.xlsx
+++ b/docs/dominio-metrico/migracion/cuestionarios/el-conde-de-sex.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="578" uniqueCount="178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="573" uniqueCount="173">
   <si>
     <t>Migración métrica · El conde de Sex</t>
   </si>
@@ -27,7 +27,7 @@
     <t>El Excel tiene cinco pestañas. En tres de ellas hay que escribir —Responder, Confirmar y Desviaciones— y las otras dos son de consulta: Secuencias, con todo lo que tiene anotado tu obra, e Instrucciones, donde estás ahora. Solo hace falta escribir en las columnas de fondo amarillo, que son «Respuesta», «Excepciones / detalle» y «Comentario». El resto de columnas las genera el programa y las necesita tal cual para poder leer las respuestas, así que conviene no tocarlas.</t>
   </si>
   <si>
-    <t>En Responder están las preguntas que no he podido contestar con lo que ya tenías anotado. Cada fila corresponde a un pasaje y a una pregunta, también cuando la pregunta es de cada estrofa: se contesta una vez y la respuesta vale para todas, y las estrofas que se aparten se anotan en «Excepciones / detalle» como «versos: esquema», por ejemplo «191-194: abab; 203-206: abab». Cuando la celda tiene desplegable, basta con elegir; cuando no, la columna «Cómo contestar» explica el formato.</t>
+    <t>En Responder están las preguntas que no he podido contestar con lo que ya tenías anotado. Cada fila corresponde a un pasaje y a una pregunta, también cuando la pregunta es de cada estrofa: se contesta una vez y la respuesta vale para todas, y las estrofas que se aparten se anotan en «Excepciones / detalle». Cuando la celda tiene desplegable, basta con elegir; cuando no, la columna «Cómo contestar» dice el formato y da un ejemplo.</t>
   </si>
   <si>
     <t>Las filas marcadas como Decidir señalan pasajes cuyo número de versos no encaja con la forma que tienen asignada. En ellas hay que elegir en el desplegable qué ocurre y explicarlo al lado. Si se trata de una laguna que no se contó, indica en qué verso está y cuántos versos faltan, porque los añadiré a la numeración y todo lo que viene después se desplazará. Si lo que falla es el rango, escribe el rango correcto.</t>
@@ -42,21 +42,6 @@
     <t>Si algo no está claro o no sabes cómo contestarlo, pregúntamelo antes de dejarlo a medias. Una vez hecha la migración podrás ver cada secuencia de tu obra con el editor nuevo en el dashboard y comprobar allí que la migración no dejó ningún hueco.</t>
   </si>
   <si>
-    <t>Cuando no hay desplegable, los formatos son estos:</t>
-  </si>
-  <si>
-    <t>Medidas: el número de sílabas de cada verso, en orden y separados por espacios. Por ejemplo, «7 11 7 7 11 7 11 11».</t>
-  </si>
-  <si>
-    <t>Posiciones: en qué versos de la estrofa cae el quebrado y cuántas sílabas tiene cada uno, separados por comas. Por ejemplo, «3: 4, 8: 5» quiere decir que el verso 3 tiene cuatro sílabas y el 8 tiene cinco.</t>
-  </si>
-  <si>
-    <t>Esquema de rima: una letra por verso, en mayúscula si el verso es de arte mayor y un guion si queda suelto. Por ejemplo, «aBab-B».</t>
-  </si>
-  <si>
-    <t>Excepciones: los versos de la estrofa y su esquema, separados por dos puntos, y cada estrofa de la siguiente con punto y coma. Por ejemplo, «191-194: abab; 203-206: abab». El esquema se escribe como arriba: una letra por verso, en mayúscula si el verso es de arte mayor.</t>
-  </si>
-  <si>
     <t>lista</t>
   </si>
   <si>
@@ -180,7 +165,7 @@
     <t>Esquema de rima · 8 estrofas</t>
   </si>
   <si>
-    <t>Elige en el desplegable. La respuesta vale para todas las estrofas; las que sean distintas, en «Excepciones», como «191-194: abab»</t>
+    <t>Elige en el desplegable. La respuesta vale para todas las estrofas; las que sean distintas, en «Excepciones», una detrás de otra y separadas por punto y coma, como «191-194: abab; 203-206: abab»</t>
   </si>
   <si>
     <t>R|0cbaa6dc-b3e1-4f2b-bba6-1317c0a9c141|a43860ff-566c-4a0b-b210-4572b8d7b066</t>
@@ -614,14 +599,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -970,7 +954,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A15"/>
+  <dimension ref="A1:A9"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="110" customWidth="1"/>
@@ -1014,31 +998,6 @@
     <row r="9" spans="1:1" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>7</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="3" t="s">
-        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -1057,74 +1016,74 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="B2" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C2" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="D2" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="B3" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="D3" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C4" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C5" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C6" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C7" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C8" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
     </row>
     <row r="9" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C9" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -1149,132 +1108,132 @@
     <col min="10" max="10" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="G1" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="H1" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="I1" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="J1" s="4" t="s">
         <v>32</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="H1" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="I1" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="J1" s="5" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F2" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="G2" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="J2" s="6" t="s">
         <v>39</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="G2" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="H2" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="I2" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="J2" s="7" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="3" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="I3" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="J3" s="6" t="s">
         <v>45</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="G3" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="H3" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="I3" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="J3" s="7" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="4" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="G4" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="H4" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="I4" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="J4" s="7" t="s">
-        <v>55</v>
+        <v>49</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="I4" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="J4" s="6" t="s">
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -1311,758 +1270,758 @@
     <col min="9" max="9" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="D1" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="C1" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="H1" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="I1" s="5" t="s">
-        <v>37</v>
+      <c r="E1" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="2" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="F2" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="G2" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="H2" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="I2" s="7" t="s">
-        <v>64</v>
+        <v>58</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="I2" s="6" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="3" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="I3" s="6" t="s">
         <v>65</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="F3" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="G3" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="H3" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="I3" s="7" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="4" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="F4" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="G4" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="H4" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="I4" s="7" t="s">
-        <v>72</v>
+        <v>58</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="I4" s="6" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="5" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="F5" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="G5" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="H5" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="I5" s="7" t="s">
-        <v>77</v>
+        <v>71</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="I5" s="6" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="6" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="F6" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="G6" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="H6" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="I6" s="7" t="s">
-        <v>81</v>
+        <v>75</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="I6" s="6" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="7" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="F7" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="G7" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="H7" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="I7" s="7" t="s">
-        <v>83</v>
+        <v>58</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="H7" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="I7" s="6" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="8" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="F8" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="G8" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="H8" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="I8" s="7" t="s">
-        <v>87</v>
+        <v>81</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="H8" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="I8" s="6" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="9" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="F9" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="G9" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="H9" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="I9" s="7" t="s">
-        <v>90</v>
+        <v>71</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="H9" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="I9" s="6" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="10" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="F10" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="G10" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="H10" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="I10" s="7" t="s">
-        <v>92</v>
+        <v>81</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="H10" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="I10" s="6" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="11" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="F11" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="G11" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="H11" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="I11" s="7" t="s">
-        <v>94</v>
+        <v>71</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="H11" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="I11" s="6" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="12" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="F12" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="G12" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="H12" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="I12" s="7" t="s">
-        <v>96</v>
+        <v>81</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="G12" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="H12" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="I12" s="6" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="13" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="F13" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="G13" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="H13" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="I13" s="7" t="s">
-        <v>98</v>
+        <v>81</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="G13" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="H13" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="I13" s="6" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="14" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="F14" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="G14" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="H14" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="I14" s="7" t="s">
-        <v>100</v>
+        <v>81</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="G14" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="H14" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="I14" s="6" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="15" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="G15" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="H15" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="I15" s="6" t="s">
         <v>101</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="F15" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="G15" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="H15" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="I15" s="7" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="16" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="F16" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="G16" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="H16" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="I16" s="7" t="s">
-        <v>108</v>
+        <v>81</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="G16" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="H16" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="I16" s="6" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="17" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="E17" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="G17" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="H17" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="I17" s="6" t="s">
         <v>105</v>
-      </c>
-      <c r="F17" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="G17" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="H17" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="I17" s="7" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="18" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="F18" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="G18" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="H18" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="I18" s="7" t="s">
-        <v>112</v>
+        <v>81</v>
+      </c>
+      <c r="F18" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="G18" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="H18" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="I18" s="6" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="19" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="F19" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="G19" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="H19" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="I19" s="7" t="s">
-        <v>115</v>
+        <v>71</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="G19" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="H19" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="I19" s="6" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="20" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="F20" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="G20" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="H20" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="I20" s="7" t="s">
-        <v>119</v>
+        <v>113</v>
+      </c>
+      <c r="F20" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="G20" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="H20" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="I20" s="6" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="21" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="F21" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="G21" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="H21" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="I21" s="7" t="s">
-        <v>124</v>
+        <v>118</v>
+      </c>
+      <c r="F21" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="G21" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="H21" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="I21" s="6" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="22" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="F22" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="G22" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="H22" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="I22" s="7" t="s">
-        <v>128</v>
+        <v>122</v>
+      </c>
+      <c r="F22" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="G22" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="H22" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="I22" s="6" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="23" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="F23" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="G23" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="H23" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="I23" s="7" t="s">
-        <v>130</v>
+        <v>122</v>
+      </c>
+      <c r="F23" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="G23" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="H23" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="I23" s="6" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="24" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="F24" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="G24" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="H24" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="I24" s="7" t="s">
-        <v>134</v>
+        <v>128</v>
+      </c>
+      <c r="F24" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="G24" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="H24" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="I24" s="6" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="25" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="F25" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="G25" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="H25" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="I25" s="7" t="s">
-        <v>136</v>
+        <v>81</v>
+      </c>
+      <c r="F25" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="G25" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="H25" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="I25" s="6" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="26" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="F26" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="G26" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="H26" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="I26" s="7" t="s">
-        <v>137</v>
+        <v>113</v>
+      </c>
+      <c r="F26" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="G26" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="H26" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="I26" s="6" t="s">
+        <v>132</v>
       </c>
     </row>
   </sheetData>
@@ -2097,36 +2056,36 @@
     <col min="10" max="10" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="C1" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>139</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>140</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="H1" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="I1" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="J1" s="5" t="s">
-        <v>37</v>
+    <row r="1" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -2154,39 +2113,39 @@
     <col min="11" max="11" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:11" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="I1" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="B1" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="C1" s="5" t="s">
+      <c r="J1" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="4" t="s">
         <v>144</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>145</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="H1" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="I1" s="5" t="s">
-        <v>148</v>
-      </c>
-      <c r="J1" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="K1" s="5" t="s">
-        <v>149</v>
       </c>
     </row>
     <row r="2" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2194,34 +2153,34 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="C2" s="3">
         <v>114</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
     </row>
     <row r="3" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2229,34 +2188,34 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="C3" s="3">
         <v>126</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="G3" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="K3" s="3" t="s">
         <v>152</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="I3" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="K3" s="3" t="s">
-        <v>157</v>
       </c>
     </row>
     <row r="4" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2264,34 +2223,34 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="C4" s="3">
         <v>52</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
     </row>
     <row r="5" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2299,34 +2258,34 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="C5" s="3">
         <v>72</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="G5" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="K5" s="3" t="s">
         <v>152</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="I5" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="K5" s="3" t="s">
-        <v>157</v>
       </c>
     </row>
     <row r="6" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2334,34 +2293,34 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="C6" s="3">
         <v>452</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
     </row>
     <row r="7" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2369,34 +2328,34 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="C7" s="3">
         <v>178</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
     </row>
     <row r="8" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2404,34 +2363,34 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="C8" s="3">
         <v>82</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
     </row>
     <row r="9" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2439,34 +2398,34 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="C9" s="3">
         <v>180</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="G9" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="K9" s="3" t="s">
         <v>152</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="K9" s="3" t="s">
-        <v>157</v>
       </c>
     </row>
     <row r="10" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2474,34 +2433,34 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="C10" s="3">
         <v>44</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
     </row>
     <row r="11" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2509,34 +2468,34 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="C11" s="3">
         <v>4</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="G11" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="K11" s="3" t="s">
         <v>152</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="I11" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="J11" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="K11" s="3" t="s">
-        <v>157</v>
       </c>
     </row>
     <row r="12" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2544,34 +2503,34 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="C12" s="3">
         <v>18</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
     </row>
     <row r="13" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2579,34 +2538,34 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="C13" s="3">
         <v>4</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="E13" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="I13" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="F13" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="G13" s="3" t="s">
+      <c r="J13" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="K13" s="3" t="s">
         <v>152</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="I13" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="J13" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="K13" s="3" t="s">
-        <v>157</v>
       </c>
     </row>
     <row r="14" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2614,34 +2573,34 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="C14" s="3">
         <v>2</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
     </row>
     <row r="15" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2649,34 +2608,34 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="C15" s="3">
         <v>40</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="G15" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="K15" s="3" t="s">
         <v>152</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="J15" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="K15" s="3" t="s">
-        <v>157</v>
       </c>
     </row>
     <row r="16" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2684,34 +2643,34 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="C16" s="3">
         <v>70</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
     </row>
     <row r="17" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2719,34 +2678,34 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="C17" s="3">
         <v>14</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="G17" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="K17" s="3" t="s">
         <v>152</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="I17" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="J17" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="K17" s="3" t="s">
-        <v>157</v>
       </c>
     </row>
     <row r="18" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2754,34 +2713,34 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="C18" s="3">
         <v>2</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="K18" s="3" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
     </row>
     <row r="19" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2789,34 +2748,34 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="C19" s="3">
         <v>14</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="G19" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="I19" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J19" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="K19" s="3" t="s">
         <v>152</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="I19" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="J19" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="K19" s="3" t="s">
-        <v>157</v>
       </c>
     </row>
     <row r="20" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2824,34 +2783,34 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="C20" s="3">
         <v>86</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="K20" s="3" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
     </row>
     <row r="21" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2859,34 +2818,34 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="C21" s="3">
         <v>80</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="G21" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J21" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="K21" s="3" t="s">
         <v>152</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="K21" s="3" t="s">
-        <v>157</v>
       </c>
     </row>
     <row r="22" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2894,34 +2853,34 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="C22" s="3">
         <v>252</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="K22" s="3" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
     </row>
     <row r="23" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2929,34 +2888,34 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="C23" s="3">
         <v>2</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="G23" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="I23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J23" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="K23" s="3" t="s">
         <v>152</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="I23" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="J23" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="K23" s="3" t="s">
-        <v>157</v>
       </c>
     </row>
     <row r="24" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2964,34 +2923,34 @@
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="C24" s="3">
         <v>142</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="K24" s="3" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
     </row>
     <row r="25" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2999,34 +2958,34 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="C25" s="3">
         <v>110</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="G25" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="H25" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="I25" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J25" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="K25" s="3" t="s">
         <v>152</v>
-      </c>
-      <c r="H25" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="I25" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="J25" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="K25" s="3" t="s">
-        <v>157</v>
       </c>
     </row>
     <row r="26" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3034,34 +2993,34 @@
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="C26" s="3">
         <v>176</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="K26" s="3" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
     </row>
     <row r="27" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3069,34 +3028,34 @@
         <v>26</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="C27" s="3">
         <v>120</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="K27" s="3" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
     </row>
     <row r="28" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3104,34 +3063,34 @@
         <v>27</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="C28" s="3">
         <v>468</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="K28" s="3" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
     </row>
     <row r="29" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3139,34 +3098,34 @@
         <v>28</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="C29" s="3">
         <v>189</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="K29" s="3" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
     </row>
   </sheetData>
